--- a/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
+++ b/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="690">
   <si>
     <t>Tên Siêu thị</t>
   </si>
@@ -709,6 +709,9 @@
     <t>KFM_HCM_Q7 - A255 (Green View)</t>
   </si>
   <si>
+    <t>KFM_HCM_Q01 - Vinhomes Golden River</t>
+  </si>
+  <si>
     <t>A101</t>
   </si>
   <si>
@@ -1390,6 +1393,9 @@
     <t>A255</t>
   </si>
   <si>
+    <t>A222</t>
+  </si>
+  <si>
     <t>-4970846623</t>
   </si>
   <si>
@@ -2075,6 +2081,9 @@
   </si>
   <si>
     <t>-1003991560755</t>
+  </si>
+  <si>
+    <t>-1004368025959</t>
   </si>
 </sst>
 </file>
@@ -2406,7 +2415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D230"/>
+  <dimension ref="A1:D231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2428,13 +2437,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2442,13 +2451,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2456,13 +2465,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D4" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2470,13 +2479,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D5" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2484,13 +2493,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D6" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2498,13 +2507,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2512,13 +2521,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D8" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2526,13 +2535,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D9" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2540,13 +2549,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D10" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2554,13 +2563,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D11" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2568,13 +2577,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D12" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2582,13 +2591,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D13" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2596,13 +2605,13 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D14" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2610,13 +2619,13 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D15" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2624,13 +2633,13 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D16" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2638,13 +2647,13 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D17" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2652,13 +2661,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D18" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2666,13 +2675,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D19" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2680,13 +2689,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C20" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D20" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2694,13 +2703,13 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D21" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2708,13 +2717,13 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C22" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D22" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2722,13 +2731,13 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C23" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D23" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2736,13 +2745,13 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C24" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D24" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2750,13 +2759,13 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C25" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D25" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2764,13 +2773,13 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D26" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2778,13 +2787,13 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C27" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D27" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2792,13 +2801,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C28" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D28" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2806,13 +2815,13 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C29" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D29" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2820,13 +2829,13 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C30" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D30" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2834,13 +2843,13 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2848,13 +2857,13 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D32" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2862,13 +2871,13 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2876,13 +2885,13 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2890,13 +2899,13 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C35" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D35" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2904,13 +2913,13 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C36" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2918,13 +2927,13 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C37" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2932,13 +2941,13 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C38" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D38" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2946,13 +2955,13 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C39" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D39" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2960,13 +2969,13 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C40" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D40" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2974,13 +2983,13 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D41" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2988,13 +2997,13 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C42" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D42" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3002,13 +3011,13 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C43" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D43" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3016,13 +3025,13 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C44" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D44" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3030,13 +3039,13 @@
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C45" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D45" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3044,13 +3053,13 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C46" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D46" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3058,13 +3067,13 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C47" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D47" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3072,13 +3081,13 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C48" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D48" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3086,13 +3095,13 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C49" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D49" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3100,13 +3109,13 @@
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C50" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D50" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3114,13 +3123,13 @@
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C51" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D51" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3128,13 +3137,13 @@
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C52" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D52" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3142,13 +3151,13 @@
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C53" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D53" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3156,13 +3165,13 @@
         <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C54" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D54" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3170,13 +3179,13 @@
         <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C55" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D55" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3184,13 +3193,13 @@
         <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C56" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D56" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3198,13 +3207,13 @@
         <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C57" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D57" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3212,13 +3221,13 @@
         <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C58" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D58" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3226,13 +3235,13 @@
         <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C59" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D59" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3240,13 +3249,13 @@
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C60" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D60" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3254,13 +3263,13 @@
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C61" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D61" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3268,13 +3277,13 @@
         <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C62" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D62" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3282,13 +3291,13 @@
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C63" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D63" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3296,13 +3305,13 @@
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C64" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D64" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3310,13 +3319,13 @@
         <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C65" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D65" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3324,13 +3333,13 @@
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C66" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D66" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3338,13 +3347,13 @@
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C67" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D67" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3352,13 +3361,13 @@
         <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C68" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D68" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3366,13 +3375,13 @@
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C69" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D69" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3380,13 +3389,13 @@
         <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C70" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D70" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3394,13 +3403,13 @@
         <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C71" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D71" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3408,13 +3417,13 @@
         <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C72" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D72" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3422,13 +3431,13 @@
         <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C73" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D73" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3436,13 +3445,13 @@
         <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C74" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D74" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3450,13 +3459,13 @@
         <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C75" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D75" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3464,13 +3473,13 @@
         <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C76" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D76" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3478,13 +3487,13 @@
         <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C77" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D77" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3492,13 +3501,13 @@
         <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C78" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D78" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3506,13 +3515,13 @@
         <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C79" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D79" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3520,13 +3529,13 @@
         <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C80" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D80" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3534,13 +3543,13 @@
         <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C81" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D81" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3548,13 +3557,13 @@
         <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C82" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D82" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3562,13 +3571,13 @@
         <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C83" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D83" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3576,13 +3585,13 @@
         <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C84" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D84" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3590,13 +3599,13 @@
         <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C85" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D85" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3604,13 +3613,13 @@
         <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C86" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D86" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3618,13 +3627,13 @@
         <v>87</v>
       </c>
       <c r="B87" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C87" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D87" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3632,13 +3641,13 @@
         <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C88" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D88" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3646,13 +3655,13 @@
         <v>89</v>
       </c>
       <c r="B89" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C89" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D89" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3660,13 +3669,13 @@
         <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C90" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D90" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3674,13 +3683,13 @@
         <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C91" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D91" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3688,13 +3697,13 @@
         <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C92" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D92" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3702,13 +3711,13 @@
         <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C93" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D93" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3716,13 +3725,13 @@
         <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C94" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D94" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3730,13 +3739,13 @@
         <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C95" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D95" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3744,13 +3753,13 @@
         <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C96" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D96" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3758,13 +3767,13 @@
         <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C97" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D97" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3772,13 +3781,13 @@
         <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C98" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D98" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3786,13 +3795,13 @@
         <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C99" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D99" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3800,13 +3809,13 @@
         <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C100" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D100" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3814,13 +3823,13 @@
         <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C101" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D101" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3828,13 +3837,13 @@
         <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C102" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D102" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3842,13 +3851,13 @@
         <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C103" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D103" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3856,13 +3865,13 @@
         <v>104</v>
       </c>
       <c r="B104" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C104" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D104" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3870,13 +3879,13 @@
         <v>105</v>
       </c>
       <c r="B105" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C105" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D105" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3884,13 +3893,13 @@
         <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C106" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D106" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3898,13 +3907,13 @@
         <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C107" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D107" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3912,13 +3921,13 @@
         <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C108" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D108" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3926,13 +3935,13 @@
         <v>109</v>
       </c>
       <c r="B109" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C109" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D109" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3940,13 +3949,13 @@
         <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C110" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D110" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3954,13 +3963,13 @@
         <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C111" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D111" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3968,13 +3977,13 @@
         <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C112" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D112" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3982,13 +3991,13 @@
         <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C113" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D113" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3996,13 +4005,13 @@
         <v>114</v>
       </c>
       <c r="B114" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C114" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D114" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4010,13 +4019,13 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C115" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D115" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4024,13 +4033,13 @@
         <v>116</v>
       </c>
       <c r="B116" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C116" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D116" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4038,13 +4047,13 @@
         <v>117</v>
       </c>
       <c r="B117" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C117" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D117" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4052,13 +4061,13 @@
         <v>118</v>
       </c>
       <c r="B118" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C118" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D118" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4066,13 +4075,13 @@
         <v>119</v>
       </c>
       <c r="B119" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C119" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D119" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4080,13 +4089,13 @@
         <v>120</v>
       </c>
       <c r="B120" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C120" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D120" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4094,13 +4103,13 @@
         <v>121</v>
       </c>
       <c r="B121" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C121" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D121" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4108,13 +4117,13 @@
         <v>122</v>
       </c>
       <c r="B122" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C122" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D122" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4122,13 +4131,13 @@
         <v>123</v>
       </c>
       <c r="B123" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C123" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D123" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4136,13 +4145,13 @@
         <v>124</v>
       </c>
       <c r="B124" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C124" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D124" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4150,13 +4159,13 @@
         <v>125</v>
       </c>
       <c r="B125" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C125" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D125" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4164,13 +4173,13 @@
         <v>126</v>
       </c>
       <c r="B126" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C126" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D126" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4178,13 +4187,13 @@
         <v>127</v>
       </c>
       <c r="B127" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C127" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D127" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4192,13 +4201,13 @@
         <v>128</v>
       </c>
       <c r="B128" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C128" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D128" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4206,13 +4215,13 @@
         <v>129</v>
       </c>
       <c r="B129" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C129" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D129" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4220,13 +4229,13 @@
         <v>130</v>
       </c>
       <c r="B130" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C130" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D130" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4234,13 +4243,13 @@
         <v>131</v>
       </c>
       <c r="B131" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C131" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D131" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4248,13 +4257,13 @@
         <v>132</v>
       </c>
       <c r="B132" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C132" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D132" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4262,13 +4271,13 @@
         <v>133</v>
       </c>
       <c r="B133" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C133" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D133" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4276,13 +4285,13 @@
         <v>134</v>
       </c>
       <c r="B134" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C134" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D134" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4290,13 +4299,13 @@
         <v>135</v>
       </c>
       <c r="B135" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C135" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D135" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4304,13 +4313,13 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C136" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D136" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4318,13 +4327,13 @@
         <v>137</v>
       </c>
       <c r="B137" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C137" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D137" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4332,13 +4341,13 @@
         <v>138</v>
       </c>
       <c r="B138" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C138" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D138" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4346,13 +4355,13 @@
         <v>139</v>
       </c>
       <c r="B139" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C139" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D139" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4360,13 +4369,13 @@
         <v>140</v>
       </c>
       <c r="B140" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C140" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D140" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4374,13 +4383,13 @@
         <v>141</v>
       </c>
       <c r="B141" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C141" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D141" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4388,13 +4397,13 @@
         <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C142" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D142" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4402,13 +4411,13 @@
         <v>143</v>
       </c>
       <c r="B143" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C143" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D143" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4416,13 +4425,13 @@
         <v>144</v>
       </c>
       <c r="B144" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C144" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D144" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4430,13 +4439,13 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C145" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D145" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4444,13 +4453,13 @@
         <v>146</v>
       </c>
       <c r="B146" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C146" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D146" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4458,13 +4467,13 @@
         <v>147</v>
       </c>
       <c r="B147" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C147" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D147" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4472,13 +4481,13 @@
         <v>148</v>
       </c>
       <c r="B148" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C148" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D148" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4486,13 +4495,13 @@
         <v>149</v>
       </c>
       <c r="B149" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C149" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D149" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4500,13 +4509,13 @@
         <v>150</v>
       </c>
       <c r="B150" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C150" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D150" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4514,13 +4523,13 @@
         <v>151</v>
       </c>
       <c r="B151" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C151" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D151" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4528,13 +4537,13 @@
         <v>152</v>
       </c>
       <c r="B152" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C152" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D152" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4542,13 +4551,13 @@
         <v>153</v>
       </c>
       <c r="B153" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C153" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D153" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4556,13 +4565,13 @@
         <v>154</v>
       </c>
       <c r="B154" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C154" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D154" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4570,13 +4579,13 @@
         <v>155</v>
       </c>
       <c r="B155" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C155" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D155" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4584,13 +4593,13 @@
         <v>156</v>
       </c>
       <c r="B156" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C156" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D156" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4598,13 +4607,13 @@
         <v>157</v>
       </c>
       <c r="B157" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C157" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D157" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4612,13 +4621,13 @@
         <v>158</v>
       </c>
       <c r="B158" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C158" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D158" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4626,13 +4635,13 @@
         <v>159</v>
       </c>
       <c r="B159" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C159" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D159" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4640,13 +4649,13 @@
         <v>160</v>
       </c>
       <c r="B160" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C160" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D160" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4654,13 +4663,13 @@
         <v>161</v>
       </c>
       <c r="B161" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C161" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D161" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4668,13 +4677,13 @@
         <v>162</v>
       </c>
       <c r="B162" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C162" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D162" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4682,13 +4691,13 @@
         <v>163</v>
       </c>
       <c r="B163" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C163" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D163" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4696,13 +4705,13 @@
         <v>164</v>
       </c>
       <c r="B164" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C164" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D164" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4710,13 +4719,13 @@
         <v>165</v>
       </c>
       <c r="B165" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C165" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D165" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4724,13 +4733,13 @@
         <v>166</v>
       </c>
       <c r="B166" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C166" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D166" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4738,13 +4747,13 @@
         <v>167</v>
       </c>
       <c r="B167" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C167" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D167" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4752,13 +4761,13 @@
         <v>168</v>
       </c>
       <c r="B168" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C168" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D168" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4766,13 +4775,13 @@
         <v>169</v>
       </c>
       <c r="B169" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C169" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D169" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4780,13 +4789,13 @@
         <v>170</v>
       </c>
       <c r="B170" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C170" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D170" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4794,13 +4803,13 @@
         <v>171</v>
       </c>
       <c r="B171" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C171" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D171" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4808,13 +4817,13 @@
         <v>172</v>
       </c>
       <c r="B172" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C172" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D172" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4822,13 +4831,13 @@
         <v>173</v>
       </c>
       <c r="B173" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C173" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D173" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4836,13 +4845,13 @@
         <v>174</v>
       </c>
       <c r="B174" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C174" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D174" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4850,13 +4859,13 @@
         <v>175</v>
       </c>
       <c r="B175" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C175" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D175" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4864,13 +4873,13 @@
         <v>176</v>
       </c>
       <c r="B176" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C176" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D176" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4878,13 +4887,13 @@
         <v>177</v>
       </c>
       <c r="B177" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C177" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D177" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4892,13 +4901,13 @@
         <v>178</v>
       </c>
       <c r="B178" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C178" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D178" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4906,13 +4915,13 @@
         <v>179</v>
       </c>
       <c r="B179" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C179" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D179" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4920,13 +4929,13 @@
         <v>180</v>
       </c>
       <c r="B180" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C180" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D180" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4934,13 +4943,13 @@
         <v>181</v>
       </c>
       <c r="B181" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C181" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D181" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4948,13 +4957,13 @@
         <v>182</v>
       </c>
       <c r="B182" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C182" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D182" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4962,13 +4971,13 @@
         <v>183</v>
       </c>
       <c r="B183" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C183" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D183" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4976,13 +4985,13 @@
         <v>184</v>
       </c>
       <c r="B184" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C184" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D184" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4990,13 +4999,13 @@
         <v>185</v>
       </c>
       <c r="B185" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C185" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D185" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5004,13 +5013,13 @@
         <v>186</v>
       </c>
       <c r="B186" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C186" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D186" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5018,13 +5027,13 @@
         <v>187</v>
       </c>
       <c r="B187" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C187" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D187" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5032,13 +5041,13 @@
         <v>188</v>
       </c>
       <c r="B188" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C188" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D188" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5046,13 +5055,13 @@
         <v>189</v>
       </c>
       <c r="B189" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C189" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D189" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5060,13 +5069,13 @@
         <v>190</v>
       </c>
       <c r="B190" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C190" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D190" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5074,13 +5083,13 @@
         <v>191</v>
       </c>
       <c r="B191" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C191" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D191" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5088,13 +5097,13 @@
         <v>192</v>
       </c>
       <c r="B192" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C192" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D192" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5102,13 +5111,13 @@
         <v>193</v>
       </c>
       <c r="B193" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C193" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D193" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5116,13 +5125,13 @@
         <v>194</v>
       </c>
       <c r="B194" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C194" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D194" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5130,13 +5139,13 @@
         <v>195</v>
       </c>
       <c r="B195" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C195" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D195" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5144,13 +5153,13 @@
         <v>196</v>
       </c>
       <c r="B196" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C196" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D196" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5158,13 +5167,13 @@
         <v>197</v>
       </c>
       <c r="B197" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C197" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D197" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5172,13 +5181,13 @@
         <v>198</v>
       </c>
       <c r="B198" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C198" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D198" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5186,13 +5195,13 @@
         <v>199</v>
       </c>
       <c r="B199" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C199" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D199" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5200,13 +5209,13 @@
         <v>200</v>
       </c>
       <c r="B200" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C200" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D200" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5214,13 +5223,13 @@
         <v>201</v>
       </c>
       <c r="B201" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C201" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D201" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5228,13 +5237,13 @@
         <v>202</v>
       </c>
       <c r="B202" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C202" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D202" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5242,13 +5251,13 @@
         <v>203</v>
       </c>
       <c r="B203" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C203" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D203" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5256,13 +5265,13 @@
         <v>204</v>
       </c>
       <c r="B204" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C204" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D204" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5270,13 +5279,13 @@
         <v>205</v>
       </c>
       <c r="B205" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C205" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D205" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5284,13 +5293,13 @@
         <v>206</v>
       </c>
       <c r="B206" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C206" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D206" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5298,13 +5307,13 @@
         <v>207</v>
       </c>
       <c r="B207" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C207" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D207" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5312,13 +5321,13 @@
         <v>208</v>
       </c>
       <c r="B208" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C208" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D208" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5326,13 +5335,13 @@
         <v>209</v>
       </c>
       <c r="B209" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C209" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D209" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5340,13 +5349,13 @@
         <v>210</v>
       </c>
       <c r="B210" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C210" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D210" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5354,13 +5363,13 @@
         <v>211</v>
       </c>
       <c r="B211" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C211" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D211" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5368,13 +5377,13 @@
         <v>212</v>
       </c>
       <c r="B212" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C212" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D212" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5382,13 +5391,13 @@
         <v>213</v>
       </c>
       <c r="B213" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C213" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D213" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5396,13 +5405,13 @@
         <v>214</v>
       </c>
       <c r="B214" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C214" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D214" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5410,13 +5419,13 @@
         <v>215</v>
       </c>
       <c r="B215" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C215" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D215" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5424,13 +5433,13 @@
         <v>216</v>
       </c>
       <c r="B216" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C216" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D216" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5438,13 +5447,13 @@
         <v>217</v>
       </c>
       <c r="B217" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C217" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D217" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5452,13 +5461,13 @@
         <v>218</v>
       </c>
       <c r="B218" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C218" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D218" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5466,13 +5475,13 @@
         <v>219</v>
       </c>
       <c r="B219" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C219" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D219" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5480,13 +5489,13 @@
         <v>220</v>
       </c>
       <c r="B220" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C220" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D220" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5494,13 +5503,13 @@
         <v>221</v>
       </c>
       <c r="B221" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C221" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D221" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5508,13 +5517,13 @@
         <v>222</v>
       </c>
       <c r="B222" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C222" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D222" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5522,13 +5531,13 @@
         <v>223</v>
       </c>
       <c r="B223" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C223" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D223" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5536,13 +5545,13 @@
         <v>224</v>
       </c>
       <c r="B224" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C224" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D224" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5550,13 +5559,13 @@
         <v>225</v>
       </c>
       <c r="B225" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C225" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D225" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5564,13 +5573,13 @@
         <v>226</v>
       </c>
       <c r="B226" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C226" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D226" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5578,13 +5587,13 @@
         <v>227</v>
       </c>
       <c r="B227" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C227" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D227" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5592,13 +5601,13 @@
         <v>228</v>
       </c>
       <c r="B228" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C228" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D228" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5606,13 +5615,13 @@
         <v>229</v>
       </c>
       <c r="B229" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C229" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D229" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5620,13 +5629,27 @@
         <v>230</v>
       </c>
       <c r="B230" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C230" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D230" t="s">
-        <v>686</v>
+        <v>688</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" t="s">
+        <v>231</v>
+      </c>
+      <c r="B231" t="s">
+        <v>459</v>
+      </c>
+      <c r="C231" t="s">
+        <v>459</v>
+      </c>
+      <c r="D231" t="s">
+        <v>689</v>
       </c>
     </row>
   </sheetData>

--- a/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
+++ b/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="693">
   <si>
     <t>Tên Siêu thị</t>
   </si>
@@ -712,6 +712,9 @@
     <t>KFM_HCM_Q01 - Vinhomes Golden River</t>
   </si>
   <si>
+    <t>KFM_BDU_TAN - 275 D33 KDC Viet Sing</t>
+  </si>
+  <si>
     <t>A101</t>
   </si>
   <si>
@@ -1396,6 +1399,9 @@
     <t>A222</t>
   </si>
   <si>
+    <t>A259</t>
+  </si>
+  <si>
     <t>-4970846623</t>
   </si>
   <si>
@@ -2084,6 +2090,9 @@
   </si>
   <si>
     <t>-1004368025959</t>
+  </si>
+  <si>
+    <t>-1004469485931</t>
   </si>
 </sst>
 </file>
@@ -2415,7 +2424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D231"/>
+  <dimension ref="A1:D232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2437,13 +2446,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2451,13 +2460,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2465,13 +2474,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D4" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2479,13 +2488,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D5" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2493,13 +2502,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D6" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2507,13 +2516,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2521,13 +2530,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D8" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2535,13 +2544,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D9" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2549,13 +2558,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D10" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2563,13 +2572,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D11" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2577,13 +2586,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D12" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2591,13 +2600,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D13" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2605,13 +2614,13 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D14" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2619,13 +2628,13 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D15" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2633,13 +2642,13 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D16" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2647,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D17" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2661,13 +2670,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D18" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2675,13 +2684,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D19" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2689,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D20" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2703,13 +2712,13 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C21" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D21" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2717,13 +2726,13 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D22" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2731,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C23" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D23" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2745,13 +2754,13 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C24" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D24" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2759,13 +2768,13 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D25" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2773,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D26" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2787,13 +2796,13 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C27" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D27" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2801,13 +2810,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D28" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2815,13 +2824,13 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D29" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2829,13 +2838,13 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C30" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D30" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2843,13 +2852,13 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D31" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2857,13 +2866,13 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C32" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2871,13 +2880,13 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C33" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D33" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2885,13 +2894,13 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2899,13 +2908,13 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C35" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2913,13 +2922,13 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C36" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D36" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2927,13 +2936,13 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C37" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D37" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2941,13 +2950,13 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C38" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D38" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2955,13 +2964,13 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C39" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2969,13 +2978,13 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C40" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D40" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2983,13 +2992,13 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C41" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D41" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2997,13 +3006,13 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C42" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D42" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3011,13 +3020,13 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C43" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D43" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3025,13 +3034,13 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C44" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D44" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3039,13 +3048,13 @@
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C45" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D45" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3053,13 +3062,13 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C46" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D46" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3067,13 +3076,13 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C47" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D47" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3081,13 +3090,13 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C48" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D48" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3095,13 +3104,13 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C49" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D49" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3109,13 +3118,13 @@
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D50" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3123,13 +3132,13 @@
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D51" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3137,13 +3146,13 @@
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D52" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3151,13 +3160,13 @@
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C53" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D53" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3165,13 +3174,13 @@
         <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C54" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D54" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3179,13 +3188,13 @@
         <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C55" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D55" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3193,13 +3202,13 @@
         <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C56" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D56" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3207,13 +3216,13 @@
         <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C57" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D57" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3221,13 +3230,13 @@
         <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C58" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D58" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3235,13 +3244,13 @@
         <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C59" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D59" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3249,13 +3258,13 @@
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C60" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D60" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3263,13 +3272,13 @@
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C61" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D61" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3277,13 +3286,13 @@
         <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C62" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D62" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3291,13 +3300,13 @@
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C63" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D63" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3305,13 +3314,13 @@
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C64" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D64" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3319,13 +3328,13 @@
         <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C65" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D65" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3333,13 +3342,13 @@
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C66" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D66" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3347,13 +3356,13 @@
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C67" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D67" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3361,13 +3370,13 @@
         <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C68" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D68" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3375,13 +3384,13 @@
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C69" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D69" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3389,13 +3398,13 @@
         <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C70" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D70" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3403,13 +3412,13 @@
         <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C71" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D71" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3417,13 +3426,13 @@
         <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C72" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D72" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3431,13 +3440,13 @@
         <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C73" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D73" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3445,13 +3454,13 @@
         <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C74" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D74" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3459,13 +3468,13 @@
         <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C75" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D75" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3473,13 +3482,13 @@
         <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C76" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D76" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3487,13 +3496,13 @@
         <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C77" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D77" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3501,13 +3510,13 @@
         <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C78" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D78" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3515,13 +3524,13 @@
         <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C79" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D79" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3529,13 +3538,13 @@
         <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C80" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D80" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3543,13 +3552,13 @@
         <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C81" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D81" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3557,13 +3566,13 @@
         <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C82" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D82" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3571,13 +3580,13 @@
         <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C83" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D83" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3585,13 +3594,13 @@
         <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C84" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D84" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3599,13 +3608,13 @@
         <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C85" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D85" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3613,13 +3622,13 @@
         <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C86" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D86" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3627,13 +3636,13 @@
         <v>87</v>
       </c>
       <c r="B87" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C87" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D87" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3641,13 +3650,13 @@
         <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C88" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D88" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3655,13 +3664,13 @@
         <v>89</v>
       </c>
       <c r="B89" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C89" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D89" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3669,13 +3678,13 @@
         <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C90" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D90" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3683,13 +3692,13 @@
         <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C91" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D91" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3697,13 +3706,13 @@
         <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C92" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D92" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3711,13 +3720,13 @@
         <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C93" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D93" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3725,13 +3734,13 @@
         <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C94" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D94" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3739,13 +3748,13 @@
         <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C95" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D95" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3753,13 +3762,13 @@
         <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C96" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D96" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3767,13 +3776,13 @@
         <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C97" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D97" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3781,13 +3790,13 @@
         <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C98" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D98" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3795,13 +3804,13 @@
         <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C99" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D99" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3809,13 +3818,13 @@
         <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C100" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D100" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3823,13 +3832,13 @@
         <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C101" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D101" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3837,13 +3846,13 @@
         <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C102" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D102" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3851,13 +3860,13 @@
         <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C103" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D103" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3865,13 +3874,13 @@
         <v>104</v>
       </c>
       <c r="B104" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C104" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D104" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3879,13 +3888,13 @@
         <v>105</v>
       </c>
       <c r="B105" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C105" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D105" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3893,13 +3902,13 @@
         <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C106" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D106" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3907,13 +3916,13 @@
         <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C107" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D107" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3921,13 +3930,13 @@
         <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C108" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D108" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3935,13 +3944,13 @@
         <v>109</v>
       </c>
       <c r="B109" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C109" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D109" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3949,13 +3958,13 @@
         <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C110" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D110" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3963,13 +3972,13 @@
         <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C111" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D111" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3977,13 +3986,13 @@
         <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C112" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D112" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3991,13 +4000,13 @@
         <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C113" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D113" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4005,13 +4014,13 @@
         <v>114</v>
       </c>
       <c r="B114" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C114" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D114" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4019,13 +4028,13 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C115" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D115" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4033,13 +4042,13 @@
         <v>116</v>
       </c>
       <c r="B116" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C116" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D116" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4047,13 +4056,13 @@
         <v>117</v>
       </c>
       <c r="B117" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C117" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D117" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4061,13 +4070,13 @@
         <v>118</v>
       </c>
       <c r="B118" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C118" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D118" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4075,13 +4084,13 @@
         <v>119</v>
       </c>
       <c r="B119" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C119" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D119" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4089,13 +4098,13 @@
         <v>120</v>
       </c>
       <c r="B120" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C120" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D120" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4103,13 +4112,13 @@
         <v>121</v>
       </c>
       <c r="B121" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C121" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D121" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4117,13 +4126,13 @@
         <v>122</v>
       </c>
       <c r="B122" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C122" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D122" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4131,13 +4140,13 @@
         <v>123</v>
       </c>
       <c r="B123" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C123" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D123" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4145,13 +4154,13 @@
         <v>124</v>
       </c>
       <c r="B124" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C124" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D124" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4159,13 +4168,13 @@
         <v>125</v>
       </c>
       <c r="B125" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C125" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D125" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4173,13 +4182,13 @@
         <v>126</v>
       </c>
       <c r="B126" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C126" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D126" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4187,13 +4196,13 @@
         <v>127</v>
       </c>
       <c r="B127" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C127" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D127" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4201,13 +4210,13 @@
         <v>128</v>
       </c>
       <c r="B128" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C128" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D128" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4215,13 +4224,13 @@
         <v>129</v>
       </c>
       <c r="B129" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C129" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D129" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4229,13 +4238,13 @@
         <v>130</v>
       </c>
       <c r="B130" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C130" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D130" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4243,13 +4252,13 @@
         <v>131</v>
       </c>
       <c r="B131" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C131" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D131" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4257,13 +4266,13 @@
         <v>132</v>
       </c>
       <c r="B132" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C132" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D132" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4271,13 +4280,13 @@
         <v>133</v>
       </c>
       <c r="B133" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C133" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D133" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4285,13 +4294,13 @@
         <v>134</v>
       </c>
       <c r="B134" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C134" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D134" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4299,13 +4308,13 @@
         <v>135</v>
       </c>
       <c r="B135" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C135" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D135" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4313,13 +4322,13 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C136" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D136" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4327,13 +4336,13 @@
         <v>137</v>
       </c>
       <c r="B137" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C137" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D137" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4341,13 +4350,13 @@
         <v>138</v>
       </c>
       <c r="B138" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C138" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D138" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4355,13 +4364,13 @@
         <v>139</v>
       </c>
       <c r="B139" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C139" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D139" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4369,13 +4378,13 @@
         <v>140</v>
       </c>
       <c r="B140" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C140" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D140" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4383,13 +4392,13 @@
         <v>141</v>
       </c>
       <c r="B141" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C141" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D141" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4397,13 +4406,13 @@
         <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C142" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D142" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4411,13 +4420,13 @@
         <v>143</v>
       </c>
       <c r="B143" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C143" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D143" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4425,13 +4434,13 @@
         <v>144</v>
       </c>
       <c r="B144" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C144" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D144" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4439,13 +4448,13 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C145" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D145" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4453,13 +4462,13 @@
         <v>146</v>
       </c>
       <c r="B146" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C146" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D146" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4467,13 +4476,13 @@
         <v>147</v>
       </c>
       <c r="B147" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C147" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D147" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4481,13 +4490,13 @@
         <v>148</v>
       </c>
       <c r="B148" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C148" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D148" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4495,13 +4504,13 @@
         <v>149</v>
       </c>
       <c r="B149" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C149" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D149" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4509,13 +4518,13 @@
         <v>150</v>
       </c>
       <c r="B150" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C150" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D150" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4523,13 +4532,13 @@
         <v>151</v>
       </c>
       <c r="B151" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C151" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D151" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4537,13 +4546,13 @@
         <v>152</v>
       </c>
       <c r="B152" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C152" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D152" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4551,13 +4560,13 @@
         <v>153</v>
       </c>
       <c r="B153" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C153" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D153" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4565,13 +4574,13 @@
         <v>154</v>
       </c>
       <c r="B154" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C154" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D154" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4579,13 +4588,13 @@
         <v>155</v>
       </c>
       <c r="B155" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C155" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D155" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4593,13 +4602,13 @@
         <v>156</v>
       </c>
       <c r="B156" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C156" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D156" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4607,13 +4616,13 @@
         <v>157</v>
       </c>
       <c r="B157" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C157" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D157" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4621,13 +4630,13 @@
         <v>158</v>
       </c>
       <c r="B158" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C158" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D158" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4635,13 +4644,13 @@
         <v>159</v>
       </c>
       <c r="B159" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C159" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D159" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4649,13 +4658,13 @@
         <v>160</v>
       </c>
       <c r="B160" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C160" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D160" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4663,13 +4672,13 @@
         <v>161</v>
       </c>
       <c r="B161" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C161" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D161" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4677,13 +4686,13 @@
         <v>162</v>
       </c>
       <c r="B162" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C162" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D162" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4691,13 +4700,13 @@
         <v>163</v>
       </c>
       <c r="B163" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C163" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D163" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4705,13 +4714,13 @@
         <v>164</v>
       </c>
       <c r="B164" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C164" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D164" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4719,13 +4728,13 @@
         <v>165</v>
       </c>
       <c r="B165" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C165" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D165" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4733,13 +4742,13 @@
         <v>166</v>
       </c>
       <c r="B166" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C166" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D166" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4747,13 +4756,13 @@
         <v>167</v>
       </c>
       <c r="B167" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C167" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D167" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4761,13 +4770,13 @@
         <v>168</v>
       </c>
       <c r="B168" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C168" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D168" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4775,13 +4784,13 @@
         <v>169</v>
       </c>
       <c r="B169" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C169" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D169" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4789,13 +4798,13 @@
         <v>170</v>
       </c>
       <c r="B170" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C170" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D170" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4803,13 +4812,13 @@
         <v>171</v>
       </c>
       <c r="B171" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C171" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D171" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4817,13 +4826,13 @@
         <v>172</v>
       </c>
       <c r="B172" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C172" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D172" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4831,13 +4840,13 @@
         <v>173</v>
       </c>
       <c r="B173" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C173" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D173" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4845,13 +4854,13 @@
         <v>174</v>
       </c>
       <c r="B174" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C174" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D174" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4859,13 +4868,13 @@
         <v>175</v>
       </c>
       <c r="B175" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C175" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D175" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4873,13 +4882,13 @@
         <v>176</v>
       </c>
       <c r="B176" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C176" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D176" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4887,13 +4896,13 @@
         <v>177</v>
       </c>
       <c r="B177" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C177" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D177" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4901,13 +4910,13 @@
         <v>178</v>
       </c>
       <c r="B178" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C178" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D178" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4915,13 +4924,13 @@
         <v>179</v>
       </c>
       <c r="B179" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C179" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D179" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4929,13 +4938,13 @@
         <v>180</v>
       </c>
       <c r="B180" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C180" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D180" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4943,13 +4952,13 @@
         <v>181</v>
       </c>
       <c r="B181" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C181" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D181" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4957,13 +4966,13 @@
         <v>182</v>
       </c>
       <c r="B182" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C182" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D182" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4971,13 +4980,13 @@
         <v>183</v>
       </c>
       <c r="B183" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C183" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D183" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4985,13 +4994,13 @@
         <v>184</v>
       </c>
       <c r="B184" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C184" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D184" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4999,13 +5008,13 @@
         <v>185</v>
       </c>
       <c r="B185" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C185" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D185" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5013,13 +5022,13 @@
         <v>186</v>
       </c>
       <c r="B186" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C186" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D186" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5027,13 +5036,13 @@
         <v>187</v>
       </c>
       <c r="B187" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C187" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D187" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5041,13 +5050,13 @@
         <v>188</v>
       </c>
       <c r="B188" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C188" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D188" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5055,13 +5064,13 @@
         <v>189</v>
       </c>
       <c r="B189" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C189" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D189" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5069,13 +5078,13 @@
         <v>190</v>
       </c>
       <c r="B190" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C190" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D190" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5083,13 +5092,13 @@
         <v>191</v>
       </c>
       <c r="B191" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C191" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D191" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5097,13 +5106,13 @@
         <v>192</v>
       </c>
       <c r="B192" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C192" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D192" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5111,13 +5120,13 @@
         <v>193</v>
       </c>
       <c r="B193" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C193" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D193" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5125,13 +5134,13 @@
         <v>194</v>
       </c>
       <c r="B194" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C194" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D194" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5139,13 +5148,13 @@
         <v>195</v>
       </c>
       <c r="B195" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C195" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D195" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5153,13 +5162,13 @@
         <v>196</v>
       </c>
       <c r="B196" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C196" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D196" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5167,13 +5176,13 @@
         <v>197</v>
       </c>
       <c r="B197" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C197" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D197" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5181,13 +5190,13 @@
         <v>198</v>
       </c>
       <c r="B198" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C198" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D198" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5195,13 +5204,13 @@
         <v>199</v>
       </c>
       <c r="B199" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C199" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D199" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5209,13 +5218,13 @@
         <v>200</v>
       </c>
       <c r="B200" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C200" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D200" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5223,13 +5232,13 @@
         <v>201</v>
       </c>
       <c r="B201" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C201" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D201" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5237,13 +5246,13 @@
         <v>202</v>
       </c>
       <c r="B202" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C202" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D202" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5251,13 +5260,13 @@
         <v>203</v>
       </c>
       <c r="B203" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C203" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D203" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5265,13 +5274,13 @@
         <v>204</v>
       </c>
       <c r="B204" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C204" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D204" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5279,13 +5288,13 @@
         <v>205</v>
       </c>
       <c r="B205" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C205" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D205" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5293,13 +5302,13 @@
         <v>206</v>
       </c>
       <c r="B206" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C206" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D206" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5307,13 +5316,13 @@
         <v>207</v>
       </c>
       <c r="B207" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C207" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D207" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5321,13 +5330,13 @@
         <v>208</v>
       </c>
       <c r="B208" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C208" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D208" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5335,13 +5344,13 @@
         <v>209</v>
       </c>
       <c r="B209" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C209" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D209" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5349,13 +5358,13 @@
         <v>210</v>
       </c>
       <c r="B210" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C210" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D210" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5363,13 +5372,13 @@
         <v>211</v>
       </c>
       <c r="B211" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C211" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D211" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5377,13 +5386,13 @@
         <v>212</v>
       </c>
       <c r="B212" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C212" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D212" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5391,13 +5400,13 @@
         <v>213</v>
       </c>
       <c r="B213" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C213" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D213" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5405,13 +5414,13 @@
         <v>214</v>
       </c>
       <c r="B214" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C214" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D214" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5419,13 +5428,13 @@
         <v>215</v>
       </c>
       <c r="B215" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C215" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D215" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5433,13 +5442,13 @@
         <v>216</v>
       </c>
       <c r="B216" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C216" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D216" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5447,13 +5456,13 @@
         <v>217</v>
       </c>
       <c r="B217" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C217" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D217" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5461,13 +5470,13 @@
         <v>218</v>
       </c>
       <c r="B218" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C218" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D218" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5475,13 +5484,13 @@
         <v>219</v>
       </c>
       <c r="B219" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C219" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D219" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5489,13 +5498,13 @@
         <v>220</v>
       </c>
       <c r="B220" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C220" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D220" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5503,13 +5512,13 @@
         <v>221</v>
       </c>
       <c r="B221" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C221" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D221" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5517,13 +5526,13 @@
         <v>222</v>
       </c>
       <c r="B222" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C222" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D222" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5531,13 +5540,13 @@
         <v>223</v>
       </c>
       <c r="B223" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C223" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D223" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5545,13 +5554,13 @@
         <v>224</v>
       </c>
       <c r="B224" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C224" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D224" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5559,13 +5568,13 @@
         <v>225</v>
       </c>
       <c r="B225" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C225" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D225" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5573,13 +5582,13 @@
         <v>226</v>
       </c>
       <c r="B226" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C226" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D226" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5587,13 +5596,13 @@
         <v>227</v>
       </c>
       <c r="B227" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C227" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D227" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5601,13 +5610,13 @@
         <v>228</v>
       </c>
       <c r="B228" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C228" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D228" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5615,13 +5624,13 @@
         <v>229</v>
       </c>
       <c r="B229" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C229" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D229" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5629,13 +5638,13 @@
         <v>230</v>
       </c>
       <c r="B230" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C230" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D230" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5643,13 +5652,27 @@
         <v>231</v>
       </c>
       <c r="B231" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C231" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D231" t="s">
-        <v>689</v>
+        <v>691</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" t="s">
+        <v>232</v>
+      </c>
+      <c r="B232" t="s">
+        <v>461</v>
+      </c>
+      <c r="C232" t="s">
+        <v>461</v>
+      </c>
+      <c r="D232" t="s">
+        <v>692</v>
       </c>
     </row>
   </sheetData>

--- a/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
+++ b/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="697">
   <si>
     <t>Tên Siêu thị</t>
   </si>
@@ -715,6 +715,12 @@
     <t>KFM_BDU_TAN - 275 D33 KDC Viet Sing</t>
   </si>
   <si>
+    <t>A246</t>
+  </si>
+  <si>
+    <t>A258</t>
+  </si>
+  <si>
     <t>A101</t>
   </si>
   <si>
@@ -2093,6 +2099,12 @@
   </si>
   <si>
     <t>-1004469485931</t>
+  </si>
+  <si>
+    <t>-1003957832728</t>
+  </si>
+  <si>
+    <t>-1004327654400</t>
   </si>
 </sst>
 </file>
@@ -2424,7 +2436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D232"/>
+  <dimension ref="A1:D234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2446,13 +2458,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2460,13 +2472,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2474,13 +2486,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2488,13 +2500,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D5" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2502,13 +2514,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D6" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2516,13 +2528,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2530,13 +2542,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D8" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2544,13 +2556,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D9" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2558,13 +2570,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2572,13 +2584,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D11" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2586,13 +2598,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D12" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2600,13 +2612,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D13" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2614,13 +2626,13 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C14" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D14" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2628,13 +2640,13 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C15" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D15" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2642,13 +2654,13 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C16" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D16" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2656,13 +2668,13 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C17" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D17" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2670,13 +2682,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C18" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D18" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2684,13 +2696,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C19" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D19" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2698,13 +2710,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C20" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D20" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2712,13 +2724,13 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C21" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D21" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2726,13 +2738,13 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C22" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D22" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2740,13 +2752,13 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C23" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D23" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2754,13 +2766,13 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C24" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D24" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2768,13 +2780,13 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C25" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D25" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2782,13 +2794,13 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C26" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D26" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2796,13 +2808,13 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C27" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D27" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2810,13 +2822,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C28" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D28" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2824,13 +2836,13 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C29" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D29" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2838,13 +2850,13 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2852,13 +2864,13 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C31" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2866,13 +2878,13 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D32" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2880,13 +2892,13 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C33" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D33" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2894,13 +2906,13 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D34" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2908,13 +2920,13 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C35" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D35" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2922,13 +2934,13 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C36" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D36" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2936,13 +2948,13 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C37" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D37" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2950,13 +2962,13 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C38" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D38" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2964,13 +2976,13 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D39" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2978,13 +2990,13 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C40" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D40" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2992,13 +3004,13 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C41" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D41" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3006,13 +3018,13 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C42" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D42" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3020,13 +3032,13 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C43" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D43" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3034,13 +3046,13 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C44" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D44" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3048,13 +3060,13 @@
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C45" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D45" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3062,13 +3074,13 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C46" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D46" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3076,13 +3088,13 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C47" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D47" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3090,13 +3102,13 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C48" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D48" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3104,13 +3116,13 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C49" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D49" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3118,13 +3130,13 @@
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C50" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D50" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3132,13 +3144,13 @@
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C51" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D51" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3146,13 +3158,13 @@
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C52" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D52" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3160,13 +3172,13 @@
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C53" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D53" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3174,13 +3186,13 @@
         <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C54" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D54" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3188,13 +3200,13 @@
         <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C55" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D55" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3202,13 +3214,13 @@
         <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C56" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D56" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3216,13 +3228,13 @@
         <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C57" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D57" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3230,13 +3242,13 @@
         <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C58" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D58" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3244,13 +3256,13 @@
         <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C59" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D59" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3258,13 +3270,13 @@
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C60" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D60" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3272,13 +3284,13 @@
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C61" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D61" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3286,13 +3298,13 @@
         <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C62" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D62" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3300,13 +3312,13 @@
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C63" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D63" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3314,13 +3326,13 @@
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C64" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D64" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3328,13 +3340,13 @@
         <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C65" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D65" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3342,13 +3354,13 @@
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C66" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D66" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3356,13 +3368,13 @@
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C67" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D67" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3370,13 +3382,13 @@
         <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C68" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D68" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3384,13 +3396,13 @@
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C69" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D69" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3398,13 +3410,13 @@
         <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C70" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D70" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3412,13 +3424,13 @@
         <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C71" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D71" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3426,13 +3438,13 @@
         <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C72" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D72" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3440,13 +3452,13 @@
         <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C73" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D73" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3454,13 +3466,13 @@
         <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C74" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D74" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3468,13 +3480,13 @@
         <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C75" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D75" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3482,13 +3494,13 @@
         <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C76" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D76" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3496,13 +3508,13 @@
         <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C77" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D77" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3510,13 +3522,13 @@
         <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C78" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D78" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3524,13 +3536,13 @@
         <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C79" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D79" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3538,13 +3550,13 @@
         <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C80" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D80" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3552,13 +3564,13 @@
         <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C81" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D81" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3566,13 +3578,13 @@
         <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C82" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D82" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3580,13 +3592,13 @@
         <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C83" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D83" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3594,13 +3606,13 @@
         <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C84" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D84" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3608,13 +3620,13 @@
         <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C85" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D85" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3622,13 +3634,13 @@
         <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C86" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D86" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3636,13 +3648,13 @@
         <v>87</v>
       </c>
       <c r="B87" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C87" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D87" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3650,13 +3662,13 @@
         <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C88" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D88" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3664,13 +3676,13 @@
         <v>89</v>
       </c>
       <c r="B89" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C89" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D89" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3678,13 +3690,13 @@
         <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C90" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D90" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3692,13 +3704,13 @@
         <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C91" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D91" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3706,13 +3718,13 @@
         <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C92" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D92" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3720,13 +3732,13 @@
         <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C93" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D93" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3734,13 +3746,13 @@
         <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C94" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D94" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3748,13 +3760,13 @@
         <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C95" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D95" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3762,13 +3774,13 @@
         <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C96" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D96" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3776,13 +3788,13 @@
         <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C97" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D97" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3790,13 +3802,13 @@
         <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C98" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D98" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3804,13 +3816,13 @@
         <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C99" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D99" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3818,13 +3830,13 @@
         <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C100" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D100" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3832,13 +3844,13 @@
         <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C101" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D101" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3846,13 +3858,13 @@
         <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C102" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D102" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3860,13 +3872,13 @@
         <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C103" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D103" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3874,13 +3886,13 @@
         <v>104</v>
       </c>
       <c r="B104" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C104" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D104" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3888,13 +3900,13 @@
         <v>105</v>
       </c>
       <c r="B105" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C105" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D105" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3902,13 +3914,13 @@
         <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C106" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D106" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3916,13 +3928,13 @@
         <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C107" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D107" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3930,13 +3942,13 @@
         <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C108" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D108" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3944,13 +3956,13 @@
         <v>109</v>
       </c>
       <c r="B109" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C109" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D109" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3958,13 +3970,13 @@
         <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C110" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D110" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3972,13 +3984,13 @@
         <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C111" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D111" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3986,13 +3998,13 @@
         <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C112" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D112" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4000,13 +4012,13 @@
         <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C113" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D113" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4014,13 +4026,13 @@
         <v>114</v>
       </c>
       <c r="B114" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C114" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D114" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4028,13 +4040,13 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C115" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D115" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4042,13 +4054,13 @@
         <v>116</v>
       </c>
       <c r="B116" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C116" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D116" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4056,13 +4068,13 @@
         <v>117</v>
       </c>
       <c r="B117" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C117" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D117" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4070,13 +4082,13 @@
         <v>118</v>
       </c>
       <c r="B118" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C118" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D118" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4084,13 +4096,13 @@
         <v>119</v>
       </c>
       <c r="B119" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C119" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D119" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4098,13 +4110,13 @@
         <v>120</v>
       </c>
       <c r="B120" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C120" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D120" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4112,13 +4124,13 @@
         <v>121</v>
       </c>
       <c r="B121" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C121" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D121" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4126,13 +4138,13 @@
         <v>122</v>
       </c>
       <c r="B122" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C122" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D122" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4140,13 +4152,13 @@
         <v>123</v>
       </c>
       <c r="B123" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C123" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D123" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4154,13 +4166,13 @@
         <v>124</v>
       </c>
       <c r="B124" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C124" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D124" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4168,13 +4180,13 @@
         <v>125</v>
       </c>
       <c r="B125" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C125" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D125" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4182,13 +4194,13 @@
         <v>126</v>
       </c>
       <c r="B126" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C126" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D126" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4196,13 +4208,13 @@
         <v>127</v>
       </c>
       <c r="B127" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C127" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D127" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4210,13 +4222,13 @@
         <v>128</v>
       </c>
       <c r="B128" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C128" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D128" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4224,13 +4236,13 @@
         <v>129</v>
       </c>
       <c r="B129" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C129" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D129" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4238,13 +4250,13 @@
         <v>130</v>
       </c>
       <c r="B130" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C130" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D130" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4252,13 +4264,13 @@
         <v>131</v>
       </c>
       <c r="B131" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C131" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D131" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4266,13 +4278,13 @@
         <v>132</v>
       </c>
       <c r="B132" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C132" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D132" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4280,13 +4292,13 @@
         <v>133</v>
       </c>
       <c r="B133" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C133" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D133" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4294,13 +4306,13 @@
         <v>134</v>
       </c>
       <c r="B134" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C134" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D134" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4308,13 +4320,13 @@
         <v>135</v>
       </c>
       <c r="B135" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C135" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D135" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4322,13 +4334,13 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C136" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D136" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4336,13 +4348,13 @@
         <v>137</v>
       </c>
       <c r="B137" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C137" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D137" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4350,13 +4362,13 @@
         <v>138</v>
       </c>
       <c r="B138" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C138" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D138" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4364,13 +4376,13 @@
         <v>139</v>
       </c>
       <c r="B139" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C139" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D139" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4378,13 +4390,13 @@
         <v>140</v>
       </c>
       <c r="B140" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C140" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D140" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4392,13 +4404,13 @@
         <v>141</v>
       </c>
       <c r="B141" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C141" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D141" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4406,13 +4418,13 @@
         <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C142" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D142" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4420,13 +4432,13 @@
         <v>143</v>
       </c>
       <c r="B143" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C143" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D143" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4434,13 +4446,13 @@
         <v>144</v>
       </c>
       <c r="B144" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C144" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D144" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4448,13 +4460,13 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C145" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D145" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4462,13 +4474,13 @@
         <v>146</v>
       </c>
       <c r="B146" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C146" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D146" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4476,13 +4488,13 @@
         <v>147</v>
       </c>
       <c r="B147" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C147" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D147" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4490,13 +4502,13 @@
         <v>148</v>
       </c>
       <c r="B148" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C148" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D148" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4504,13 +4516,13 @@
         <v>149</v>
       </c>
       <c r="B149" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C149" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D149" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4518,13 +4530,13 @@
         <v>150</v>
       </c>
       <c r="B150" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C150" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D150" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4532,13 +4544,13 @@
         <v>151</v>
       </c>
       <c r="B151" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C151" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D151" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4546,13 +4558,13 @@
         <v>152</v>
       </c>
       <c r="B152" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C152" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D152" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4560,13 +4572,13 @@
         <v>153</v>
       </c>
       <c r="B153" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C153" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D153" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4574,13 +4586,13 @@
         <v>154</v>
       </c>
       <c r="B154" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C154" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D154" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4588,13 +4600,13 @@
         <v>155</v>
       </c>
       <c r="B155" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C155" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D155" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4602,13 +4614,13 @@
         <v>156</v>
       </c>
       <c r="B156" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C156" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D156" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4616,13 +4628,13 @@
         <v>157</v>
       </c>
       <c r="B157" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C157" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D157" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4630,13 +4642,13 @@
         <v>158</v>
       </c>
       <c r="B158" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C158" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D158" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4644,13 +4656,13 @@
         <v>159</v>
       </c>
       <c r="B159" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C159" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D159" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4658,13 +4670,13 @@
         <v>160</v>
       </c>
       <c r="B160" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C160" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D160" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4672,13 +4684,13 @@
         <v>161</v>
       </c>
       <c r="B161" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C161" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D161" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4686,13 +4698,13 @@
         <v>162</v>
       </c>
       <c r="B162" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C162" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D162" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4700,13 +4712,13 @@
         <v>163</v>
       </c>
       <c r="B163" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C163" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D163" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4714,13 +4726,13 @@
         <v>164</v>
       </c>
       <c r="B164" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C164" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D164" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4728,13 +4740,13 @@
         <v>165</v>
       </c>
       <c r="B165" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C165" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D165" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4742,13 +4754,13 @@
         <v>166</v>
       </c>
       <c r="B166" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C166" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D166" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4756,13 +4768,13 @@
         <v>167</v>
       </c>
       <c r="B167" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C167" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D167" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4770,13 +4782,13 @@
         <v>168</v>
       </c>
       <c r="B168" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C168" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D168" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4784,13 +4796,13 @@
         <v>169</v>
       </c>
       <c r="B169" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C169" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D169" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4798,13 +4810,13 @@
         <v>170</v>
       </c>
       <c r="B170" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C170" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D170" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4812,13 +4824,13 @@
         <v>171</v>
       </c>
       <c r="B171" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C171" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D171" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4826,13 +4838,13 @@
         <v>172</v>
       </c>
       <c r="B172" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C172" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D172" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4840,13 +4852,13 @@
         <v>173</v>
       </c>
       <c r="B173" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C173" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D173" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4854,13 +4866,13 @@
         <v>174</v>
       </c>
       <c r="B174" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C174" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D174" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4868,13 +4880,13 @@
         <v>175</v>
       </c>
       <c r="B175" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C175" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D175" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4882,13 +4894,13 @@
         <v>176</v>
       </c>
       <c r="B176" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C176" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D176" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4896,13 +4908,13 @@
         <v>177</v>
       </c>
       <c r="B177" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C177" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D177" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4910,13 +4922,13 @@
         <v>178</v>
       </c>
       <c r="B178" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C178" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D178" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4924,13 +4936,13 @@
         <v>179</v>
       </c>
       <c r="B179" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C179" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D179" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4938,13 +4950,13 @@
         <v>180</v>
       </c>
       <c r="B180" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C180" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D180" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4952,13 +4964,13 @@
         <v>181</v>
       </c>
       <c r="B181" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C181" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D181" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4966,13 +4978,13 @@
         <v>182</v>
       </c>
       <c r="B182" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C182" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D182" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4980,13 +4992,13 @@
         <v>183</v>
       </c>
       <c r="B183" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C183" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D183" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4994,13 +5006,13 @@
         <v>184</v>
       </c>
       <c r="B184" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C184" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D184" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5008,13 +5020,13 @@
         <v>185</v>
       </c>
       <c r="B185" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C185" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D185" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5022,13 +5034,13 @@
         <v>186</v>
       </c>
       <c r="B186" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C186" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D186" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5036,13 +5048,13 @@
         <v>187</v>
       </c>
       <c r="B187" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C187" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D187" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5050,13 +5062,13 @@
         <v>188</v>
       </c>
       <c r="B188" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C188" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D188" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5064,13 +5076,13 @@
         <v>189</v>
       </c>
       <c r="B189" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C189" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D189" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5078,13 +5090,13 @@
         <v>190</v>
       </c>
       <c r="B190" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C190" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D190" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5092,13 +5104,13 @@
         <v>191</v>
       </c>
       <c r="B191" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C191" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D191" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5106,13 +5118,13 @@
         <v>192</v>
       </c>
       <c r="B192" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C192" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D192" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5120,13 +5132,13 @@
         <v>193</v>
       </c>
       <c r="B193" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C193" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D193" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5134,13 +5146,13 @@
         <v>194</v>
       </c>
       <c r="B194" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C194" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D194" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5148,13 +5160,13 @@
         <v>195</v>
       </c>
       <c r="B195" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C195" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D195" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5162,13 +5174,13 @@
         <v>196</v>
       </c>
       <c r="B196" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C196" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D196" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5176,13 +5188,13 @@
         <v>197</v>
       </c>
       <c r="B197" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C197" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D197" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5190,13 +5202,13 @@
         <v>198</v>
       </c>
       <c r="B198" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C198" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D198" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5204,13 +5216,13 @@
         <v>199</v>
       </c>
       <c r="B199" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C199" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D199" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5218,13 +5230,13 @@
         <v>200</v>
       </c>
       <c r="B200" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C200" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D200" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5232,13 +5244,13 @@
         <v>201</v>
       </c>
       <c r="B201" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C201" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D201" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5246,13 +5258,13 @@
         <v>202</v>
       </c>
       <c r="B202" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C202" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D202" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5260,13 +5272,13 @@
         <v>203</v>
       </c>
       <c r="B203" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C203" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D203" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5274,13 +5286,13 @@
         <v>204</v>
       </c>
       <c r="B204" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C204" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D204" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5288,13 +5300,13 @@
         <v>205</v>
       </c>
       <c r="B205" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C205" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D205" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5302,13 +5314,13 @@
         <v>206</v>
       </c>
       <c r="B206" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C206" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D206" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5316,13 +5328,13 @@
         <v>207</v>
       </c>
       <c r="B207" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C207" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D207" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5330,13 +5342,13 @@
         <v>208</v>
       </c>
       <c r="B208" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C208" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D208" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5344,13 +5356,13 @@
         <v>209</v>
       </c>
       <c r="B209" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C209" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D209" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5358,13 +5370,13 @@
         <v>210</v>
       </c>
       <c r="B210" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C210" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D210" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5372,13 +5384,13 @@
         <v>211</v>
       </c>
       <c r="B211" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C211" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D211" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5386,13 +5398,13 @@
         <v>212</v>
       </c>
       <c r="B212" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C212" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D212" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5400,13 +5412,13 @@
         <v>213</v>
       </c>
       <c r="B213" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C213" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D213" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5414,13 +5426,13 @@
         <v>214</v>
       </c>
       <c r="B214" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C214" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D214" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5428,13 +5440,13 @@
         <v>215</v>
       </c>
       <c r="B215" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C215" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D215" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5442,13 +5454,13 @@
         <v>216</v>
       </c>
       <c r="B216" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C216" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D216" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5456,13 +5468,13 @@
         <v>217</v>
       </c>
       <c r="B217" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C217" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D217" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5470,13 +5482,13 @@
         <v>218</v>
       </c>
       <c r="B218" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C218" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D218" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5484,13 +5496,13 @@
         <v>219</v>
       </c>
       <c r="B219" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C219" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D219" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5498,13 +5510,13 @@
         <v>220</v>
       </c>
       <c r="B220" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C220" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D220" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5512,13 +5524,13 @@
         <v>221</v>
       </c>
       <c r="B221" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C221" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D221" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5526,13 +5538,13 @@
         <v>222</v>
       </c>
       <c r="B222" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C222" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D222" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5540,13 +5552,13 @@
         <v>223</v>
       </c>
       <c r="B223" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C223" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D223" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5554,13 +5566,13 @@
         <v>224</v>
       </c>
       <c r="B224" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C224" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D224" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5568,13 +5580,13 @@
         <v>225</v>
       </c>
       <c r="B225" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C225" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D225" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5582,13 +5594,13 @@
         <v>226</v>
       </c>
       <c r="B226" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C226" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D226" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5596,13 +5608,13 @@
         <v>227</v>
       </c>
       <c r="B227" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C227" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D227" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5610,13 +5622,13 @@
         <v>228</v>
       </c>
       <c r="B228" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C228" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D228" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5624,13 +5636,13 @@
         <v>229</v>
       </c>
       <c r="B229" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C229" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D229" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5638,13 +5650,13 @@
         <v>230</v>
       </c>
       <c r="B230" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C230" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D230" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5652,13 +5664,13 @@
         <v>231</v>
       </c>
       <c r="B231" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C231" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D231" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5666,13 +5678,41 @@
         <v>232</v>
       </c>
       <c r="B232" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C232" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D232" t="s">
-        <v>692</v>
+        <v>694</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" t="s">
+        <v>233</v>
+      </c>
+      <c r="B233" t="s">
+        <v>233</v>
+      </c>
+      <c r="C233" t="s">
+        <v>233</v>
+      </c>
+      <c r="D233" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" t="s">
+        <v>234</v>
+      </c>
+      <c r="B234" t="s">
+        <v>234</v>
+      </c>
+      <c r="C234" t="s">
+        <v>234</v>
+      </c>
+      <c r="D234" t="s">
+        <v>696</v>
       </c>
     </row>
   </sheetData>

--- a/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
+++ b/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
@@ -1915,7 +1915,7 @@
     <t>-4642722927</t>
   </si>
   <si>
-    <t>-4174079222</t>
+    <t>-1004451611911</t>
   </si>
   <si>
     <t>-4832327413</t>

--- a/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
+++ b/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="700">
   <si>
     <t>Tên Siêu thị</t>
   </si>
@@ -721,6 +721,9 @@
     <t>A258</t>
   </si>
   <si>
+    <t>KFM_HNI_YHO - CT3 Yên Hoà Park View</t>
+  </si>
+  <si>
     <t>A101</t>
   </si>
   <si>
@@ -1408,6 +1411,9 @@
     <t>A259</t>
   </si>
   <si>
+    <t>B001</t>
+  </si>
+  <si>
     <t>-4970846623</t>
   </si>
   <si>
@@ -2105,6 +2111,9 @@
   </si>
   <si>
     <t>-1004327654400</t>
+  </si>
+  <si>
+    <t>-1004305022913</t>
   </si>
 </sst>
 </file>
@@ -2436,7 +2445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D234"/>
+  <dimension ref="A1:D235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2458,13 +2467,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2472,13 +2481,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2486,13 +2495,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2500,13 +2509,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D5" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2514,13 +2523,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D6" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2528,13 +2537,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D7" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2542,13 +2551,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D8" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2556,13 +2565,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D9" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2570,13 +2579,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2584,13 +2593,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D11" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2598,13 +2607,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D12" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2612,13 +2621,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D13" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2626,13 +2635,13 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D14" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2640,13 +2649,13 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D15" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2654,13 +2663,13 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D16" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2668,13 +2677,13 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D17" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2682,13 +2691,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D18" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2696,13 +2705,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D19" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2710,13 +2719,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C20" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D20" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2724,13 +2733,13 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D21" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2738,13 +2747,13 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D22" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2752,13 +2761,13 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D23" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2766,13 +2775,13 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D24" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2780,13 +2789,13 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D25" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2794,13 +2803,13 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D26" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2808,13 +2817,13 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D27" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2822,13 +2831,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D28" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2836,13 +2845,13 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2850,13 +2859,13 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C30" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D30" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2864,13 +2873,13 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D31" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2878,13 +2887,13 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C32" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2892,13 +2901,13 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D33" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2906,13 +2915,13 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2920,13 +2929,13 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C35" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D35" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2934,13 +2943,13 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C36" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D36" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2948,13 +2957,13 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C37" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D37" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2962,13 +2971,13 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C38" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D38" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2976,13 +2985,13 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C39" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D39" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2990,13 +2999,13 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C40" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D40" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3004,13 +3013,13 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C41" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D41" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3018,13 +3027,13 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C42" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D42" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3032,13 +3041,13 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C43" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D43" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3046,13 +3055,13 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C44" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D44" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3060,13 +3069,13 @@
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C45" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D45" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3074,13 +3083,13 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C46" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D46" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3088,13 +3097,13 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C47" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D47" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3102,13 +3111,13 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C48" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D48" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3116,13 +3125,13 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C49" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D49" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3130,13 +3139,13 @@
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C50" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D50" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3144,13 +3153,13 @@
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C51" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D51" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3158,13 +3167,13 @@
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C52" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D52" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3172,13 +3181,13 @@
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C53" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D53" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3186,13 +3195,13 @@
         <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C54" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D54" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3200,13 +3209,13 @@
         <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C55" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D55" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3214,13 +3223,13 @@
         <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C56" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D56" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3228,13 +3237,13 @@
         <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C57" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D57" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3242,13 +3251,13 @@
         <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C58" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D58" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3256,13 +3265,13 @@
         <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C59" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D59" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3270,13 +3279,13 @@
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C60" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D60" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3284,13 +3293,13 @@
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C61" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D61" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3298,13 +3307,13 @@
         <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C62" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D62" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3312,13 +3321,13 @@
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C63" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D63" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3326,13 +3335,13 @@
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C64" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D64" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3340,13 +3349,13 @@
         <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C65" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D65" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3354,13 +3363,13 @@
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C66" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D66" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3368,13 +3377,13 @@
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C67" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D67" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3382,13 +3391,13 @@
         <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C68" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D68" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3396,13 +3405,13 @@
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C69" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D69" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3410,13 +3419,13 @@
         <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C70" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D70" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3424,13 +3433,13 @@
         <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C71" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D71" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3438,13 +3447,13 @@
         <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C72" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D72" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3452,13 +3461,13 @@
         <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C73" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D73" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3466,13 +3475,13 @@
         <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C74" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D74" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3480,13 +3489,13 @@
         <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C75" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D75" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3494,13 +3503,13 @@
         <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C76" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D76" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3508,13 +3517,13 @@
         <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C77" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D77" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3522,13 +3531,13 @@
         <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C78" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D78" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3536,13 +3545,13 @@
         <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C79" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D79" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3550,13 +3559,13 @@
         <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C80" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D80" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3564,13 +3573,13 @@
         <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C81" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D81" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3578,13 +3587,13 @@
         <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C82" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D82" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3592,13 +3601,13 @@
         <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C83" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D83" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3606,13 +3615,13 @@
         <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C84" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D84" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3620,13 +3629,13 @@
         <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C85" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D85" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3634,13 +3643,13 @@
         <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C86" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D86" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3648,13 +3657,13 @@
         <v>87</v>
       </c>
       <c r="B87" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C87" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D87" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3662,13 +3671,13 @@
         <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C88" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D88" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3676,13 +3685,13 @@
         <v>89</v>
       </c>
       <c r="B89" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C89" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D89" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3690,13 +3699,13 @@
         <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C90" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D90" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3704,13 +3713,13 @@
         <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C91" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D91" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3718,13 +3727,13 @@
         <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C92" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D92" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3732,13 +3741,13 @@
         <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C93" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D93" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3746,13 +3755,13 @@
         <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C94" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D94" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3760,13 +3769,13 @@
         <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C95" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D95" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3774,13 +3783,13 @@
         <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C96" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D96" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3788,13 +3797,13 @@
         <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C97" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D97" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3802,13 +3811,13 @@
         <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C98" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D98" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3816,13 +3825,13 @@
         <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C99" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D99" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3830,13 +3839,13 @@
         <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C100" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D100" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3844,13 +3853,13 @@
         <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C101" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D101" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3858,13 +3867,13 @@
         <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C102" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D102" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3872,13 +3881,13 @@
         <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C103" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D103" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3886,13 +3895,13 @@
         <v>104</v>
       </c>
       <c r="B104" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C104" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D104" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3900,13 +3909,13 @@
         <v>105</v>
       </c>
       <c r="B105" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C105" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D105" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3914,13 +3923,13 @@
         <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C106" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D106" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3928,13 +3937,13 @@
         <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C107" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D107" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3942,13 +3951,13 @@
         <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C108" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D108" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3956,13 +3965,13 @@
         <v>109</v>
       </c>
       <c r="B109" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C109" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D109" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3970,13 +3979,13 @@
         <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C110" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D110" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3984,13 +3993,13 @@
         <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C111" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D111" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3998,13 +4007,13 @@
         <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C112" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D112" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4012,13 +4021,13 @@
         <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C113" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D113" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4026,13 +4035,13 @@
         <v>114</v>
       </c>
       <c r="B114" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C114" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D114" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4040,13 +4049,13 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C115" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D115" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4054,13 +4063,13 @@
         <v>116</v>
       </c>
       <c r="B116" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C116" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D116" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4068,13 +4077,13 @@
         <v>117</v>
       </c>
       <c r="B117" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C117" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D117" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4082,13 +4091,13 @@
         <v>118</v>
       </c>
       <c r="B118" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C118" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D118" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4096,13 +4105,13 @@
         <v>119</v>
       </c>
       <c r="B119" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C119" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D119" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4110,13 +4119,13 @@
         <v>120</v>
       </c>
       <c r="B120" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C120" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D120" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4124,13 +4133,13 @@
         <v>121</v>
       </c>
       <c r="B121" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C121" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D121" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4138,13 +4147,13 @@
         <v>122</v>
       </c>
       <c r="B122" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C122" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D122" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4152,13 +4161,13 @@
         <v>123</v>
       </c>
       <c r="B123" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C123" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D123" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4166,13 +4175,13 @@
         <v>124</v>
       </c>
       <c r="B124" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C124" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D124" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4180,13 +4189,13 @@
         <v>125</v>
       </c>
       <c r="B125" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C125" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D125" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4194,13 +4203,13 @@
         <v>126</v>
       </c>
       <c r="B126" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C126" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D126" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4208,13 +4217,13 @@
         <v>127</v>
       </c>
       <c r="B127" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C127" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D127" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4222,13 +4231,13 @@
         <v>128</v>
       </c>
       <c r="B128" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C128" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D128" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4236,13 +4245,13 @@
         <v>129</v>
       </c>
       <c r="B129" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C129" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D129" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4250,13 +4259,13 @@
         <v>130</v>
       </c>
       <c r="B130" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C130" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D130" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4264,13 +4273,13 @@
         <v>131</v>
       </c>
       <c r="B131" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C131" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D131" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4278,13 +4287,13 @@
         <v>132</v>
       </c>
       <c r="B132" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C132" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D132" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4292,13 +4301,13 @@
         <v>133</v>
       </c>
       <c r="B133" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C133" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D133" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4306,13 +4315,13 @@
         <v>134</v>
       </c>
       <c r="B134" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C134" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D134" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4320,13 +4329,13 @@
         <v>135</v>
       </c>
       <c r="B135" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C135" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D135" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4334,13 +4343,13 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C136" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D136" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4348,13 +4357,13 @@
         <v>137</v>
       </c>
       <c r="B137" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C137" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D137" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4362,13 +4371,13 @@
         <v>138</v>
       </c>
       <c r="B138" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C138" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D138" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4376,13 +4385,13 @@
         <v>139</v>
       </c>
       <c r="B139" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C139" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D139" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4390,13 +4399,13 @@
         <v>140</v>
       </c>
       <c r="B140" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C140" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D140" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4404,13 +4413,13 @@
         <v>141</v>
       </c>
       <c r="B141" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C141" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D141" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4418,13 +4427,13 @@
         <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C142" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D142" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4432,13 +4441,13 @@
         <v>143</v>
       </c>
       <c r="B143" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C143" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D143" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4446,13 +4455,13 @@
         <v>144</v>
       </c>
       <c r="B144" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C144" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D144" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4460,13 +4469,13 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D145" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4474,13 +4483,13 @@
         <v>146</v>
       </c>
       <c r="B146" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C146" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D146" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4488,13 +4497,13 @@
         <v>147</v>
       </c>
       <c r="B147" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C147" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D147" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4502,13 +4511,13 @@
         <v>148</v>
       </c>
       <c r="B148" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C148" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D148" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4516,13 +4525,13 @@
         <v>149</v>
       </c>
       <c r="B149" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C149" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D149" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4530,13 +4539,13 @@
         <v>150</v>
       </c>
       <c r="B150" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C150" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D150" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4544,13 +4553,13 @@
         <v>151</v>
       </c>
       <c r="B151" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C151" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D151" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4558,13 +4567,13 @@
         <v>152</v>
       </c>
       <c r="B152" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C152" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D152" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4572,13 +4581,13 @@
         <v>153</v>
       </c>
       <c r="B153" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C153" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D153" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4586,13 +4595,13 @@
         <v>154</v>
       </c>
       <c r="B154" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C154" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D154" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4600,13 +4609,13 @@
         <v>155</v>
       </c>
       <c r="B155" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C155" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D155" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4614,13 +4623,13 @@
         <v>156</v>
       </c>
       <c r="B156" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C156" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D156" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4628,13 +4637,13 @@
         <v>157</v>
       </c>
       <c r="B157" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C157" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D157" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4642,13 +4651,13 @@
         <v>158</v>
       </c>
       <c r="B158" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C158" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D158" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4656,13 +4665,13 @@
         <v>159</v>
       </c>
       <c r="B159" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C159" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D159" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4670,13 +4679,13 @@
         <v>160</v>
       </c>
       <c r="B160" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C160" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D160" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4684,13 +4693,13 @@
         <v>161</v>
       </c>
       <c r="B161" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C161" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D161" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4698,13 +4707,13 @@
         <v>162</v>
       </c>
       <c r="B162" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C162" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D162" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4712,13 +4721,13 @@
         <v>163</v>
       </c>
       <c r="B163" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C163" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D163" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4726,13 +4735,13 @@
         <v>164</v>
       </c>
       <c r="B164" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C164" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D164" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4740,13 +4749,13 @@
         <v>165</v>
       </c>
       <c r="B165" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C165" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D165" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4754,13 +4763,13 @@
         <v>166</v>
       </c>
       <c r="B166" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C166" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D166" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4768,13 +4777,13 @@
         <v>167</v>
       </c>
       <c r="B167" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C167" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D167" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4782,13 +4791,13 @@
         <v>168</v>
       </c>
       <c r="B168" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C168" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D168" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4796,13 +4805,13 @@
         <v>169</v>
       </c>
       <c r="B169" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C169" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D169" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4810,13 +4819,13 @@
         <v>170</v>
       </c>
       <c r="B170" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C170" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D170" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4824,13 +4833,13 @@
         <v>171</v>
       </c>
       <c r="B171" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C171" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D171" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4838,13 +4847,13 @@
         <v>172</v>
       </c>
       <c r="B172" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C172" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D172" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4852,13 +4861,13 @@
         <v>173</v>
       </c>
       <c r="B173" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C173" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D173" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4866,13 +4875,13 @@
         <v>174</v>
       </c>
       <c r="B174" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C174" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D174" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4880,13 +4889,13 @@
         <v>175</v>
       </c>
       <c r="B175" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C175" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D175" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4894,13 +4903,13 @@
         <v>176</v>
       </c>
       <c r="B176" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C176" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D176" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4908,13 +4917,13 @@
         <v>177</v>
       </c>
       <c r="B177" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C177" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D177" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4922,13 +4931,13 @@
         <v>178</v>
       </c>
       <c r="B178" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C178" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D178" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4936,13 +4945,13 @@
         <v>179</v>
       </c>
       <c r="B179" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C179" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D179" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4950,13 +4959,13 @@
         <v>180</v>
       </c>
       <c r="B180" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C180" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D180" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4964,13 +4973,13 @@
         <v>181</v>
       </c>
       <c r="B181" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C181" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D181" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4978,13 +4987,13 @@
         <v>182</v>
       </c>
       <c r="B182" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C182" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D182" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4992,13 +5001,13 @@
         <v>183</v>
       </c>
       <c r="B183" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C183" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D183" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5006,13 +5015,13 @@
         <v>184</v>
       </c>
       <c r="B184" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C184" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D184" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5020,13 +5029,13 @@
         <v>185</v>
       </c>
       <c r="B185" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C185" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D185" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5034,13 +5043,13 @@
         <v>186</v>
       </c>
       <c r="B186" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C186" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D186" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5048,13 +5057,13 @@
         <v>187</v>
       </c>
       <c r="B187" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C187" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D187" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5062,13 +5071,13 @@
         <v>188</v>
       </c>
       <c r="B188" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C188" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D188" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5076,13 +5085,13 @@
         <v>189</v>
       </c>
       <c r="B189" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C189" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D189" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5090,13 +5099,13 @@
         <v>190</v>
       </c>
       <c r="B190" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C190" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D190" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5104,13 +5113,13 @@
         <v>191</v>
       </c>
       <c r="B191" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C191" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D191" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5118,13 +5127,13 @@
         <v>192</v>
       </c>
       <c r="B192" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C192" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D192" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5132,13 +5141,13 @@
         <v>193</v>
       </c>
       <c r="B193" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C193" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D193" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5146,13 +5155,13 @@
         <v>194</v>
       </c>
       <c r="B194" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C194" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D194" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5160,13 +5169,13 @@
         <v>195</v>
       </c>
       <c r="B195" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C195" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D195" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5174,13 +5183,13 @@
         <v>196</v>
       </c>
       <c r="B196" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C196" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D196" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5188,13 +5197,13 @@
         <v>197</v>
       </c>
       <c r="B197" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C197" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D197" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5202,13 +5211,13 @@
         <v>198</v>
       </c>
       <c r="B198" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C198" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D198" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5216,13 +5225,13 @@
         <v>199</v>
       </c>
       <c r="B199" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C199" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D199" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5230,13 +5239,13 @@
         <v>200</v>
       </c>
       <c r="B200" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C200" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D200" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5244,13 +5253,13 @@
         <v>201</v>
       </c>
       <c r="B201" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C201" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D201" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5258,13 +5267,13 @@
         <v>202</v>
       </c>
       <c r="B202" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C202" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D202" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5272,13 +5281,13 @@
         <v>203</v>
       </c>
       <c r="B203" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C203" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D203" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5286,13 +5295,13 @@
         <v>204</v>
       </c>
       <c r="B204" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C204" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D204" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5300,13 +5309,13 @@
         <v>205</v>
       </c>
       <c r="B205" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C205" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D205" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5314,13 +5323,13 @@
         <v>206</v>
       </c>
       <c r="B206" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C206" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D206" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5328,13 +5337,13 @@
         <v>207</v>
       </c>
       <c r="B207" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C207" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D207" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5342,13 +5351,13 @@
         <v>208</v>
       </c>
       <c r="B208" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C208" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D208" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5356,13 +5365,13 @@
         <v>209</v>
       </c>
       <c r="B209" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C209" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D209" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5370,13 +5379,13 @@
         <v>210</v>
       </c>
       <c r="B210" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C210" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D210" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5384,13 +5393,13 @@
         <v>211</v>
       </c>
       <c r="B211" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C211" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D211" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5398,13 +5407,13 @@
         <v>212</v>
       </c>
       <c r="B212" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C212" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D212" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5412,13 +5421,13 @@
         <v>213</v>
       </c>
       <c r="B213" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C213" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D213" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5426,13 +5435,13 @@
         <v>214</v>
       </c>
       <c r="B214" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C214" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D214" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5440,13 +5449,13 @@
         <v>215</v>
       </c>
       <c r="B215" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C215" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D215" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5454,13 +5463,13 @@
         <v>216</v>
       </c>
       <c r="B216" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C216" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D216" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5468,13 +5477,13 @@
         <v>217</v>
       </c>
       <c r="B217" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C217" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D217" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5482,13 +5491,13 @@
         <v>218</v>
       </c>
       <c r="B218" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C218" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D218" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5496,13 +5505,13 @@
         <v>219</v>
       </c>
       <c r="B219" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C219" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D219" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5510,13 +5519,13 @@
         <v>220</v>
       </c>
       <c r="B220" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C220" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D220" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5524,13 +5533,13 @@
         <v>221</v>
       </c>
       <c r="B221" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C221" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D221" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5538,13 +5547,13 @@
         <v>222</v>
       </c>
       <c r="B222" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C222" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D222" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5552,13 +5561,13 @@
         <v>223</v>
       </c>
       <c r="B223" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C223" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D223" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5566,13 +5575,13 @@
         <v>224</v>
       </c>
       <c r="B224" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C224" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D224" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5580,13 +5589,13 @@
         <v>225</v>
       </c>
       <c r="B225" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C225" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D225" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5594,13 +5603,13 @@
         <v>226</v>
       </c>
       <c r="B226" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C226" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D226" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5608,13 +5617,13 @@
         <v>227</v>
       </c>
       <c r="B227" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C227" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D227" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5622,13 +5631,13 @@
         <v>228</v>
       </c>
       <c r="B228" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C228" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D228" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5636,13 +5645,13 @@
         <v>229</v>
       </c>
       <c r="B229" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C229" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D229" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5650,13 +5659,13 @@
         <v>230</v>
       </c>
       <c r="B230" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C230" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D230" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5664,13 +5673,13 @@
         <v>231</v>
       </c>
       <c r="B231" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C231" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D231" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5678,13 +5687,13 @@
         <v>232</v>
       </c>
       <c r="B232" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C232" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D232" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5698,7 +5707,7 @@
         <v>233</v>
       </c>
       <c r="D233" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5712,7 +5721,21 @@
         <v>234</v>
       </c>
       <c r="D234" t="s">
-        <v>696</v>
+        <v>698</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" t="s">
+        <v>235</v>
+      </c>
+      <c r="B235" t="s">
+        <v>465</v>
+      </c>
+      <c r="C235" t="s">
+        <v>465</v>
+      </c>
+      <c r="D235" t="s">
+        <v>699</v>
       </c>
     </row>
   </sheetData>

--- a/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
+++ b/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="703">
   <si>
     <t>Tên Siêu thị</t>
   </si>
@@ -724,6 +724,9 @@
     <t>KFM_HNI_YHO - CT3 Yên Hoà Park View</t>
   </si>
   <si>
+    <t>KFM_HCM_PNH - Hoa Sứ</t>
+  </si>
+  <si>
     <t>A101</t>
   </si>
   <si>
@@ -1414,6 +1417,9 @@
     <t>B001</t>
   </si>
   <si>
+    <t>A266</t>
+  </si>
+  <si>
     <t>-4970846623</t>
   </si>
   <si>
@@ -2114,6 +2120,9 @@
   </si>
   <si>
     <t>-1004305022913</t>
+  </si>
+  <si>
+    <t>-1004376355185</t>
   </si>
 </sst>
 </file>
@@ -2445,7 +2454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D235"/>
+  <dimension ref="A1:D236"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2467,13 +2476,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2481,13 +2490,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2495,13 +2504,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D4" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2509,13 +2518,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D5" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2523,13 +2532,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D6" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2537,13 +2546,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D7" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2551,13 +2560,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D8" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2565,13 +2574,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D9" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2579,13 +2588,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D10" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2593,13 +2602,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D11" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2607,13 +2616,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D12" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2621,13 +2630,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D13" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2635,13 +2644,13 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D14" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2649,13 +2658,13 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D15" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2663,13 +2672,13 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C16" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D16" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2677,13 +2686,13 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D17" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2691,13 +2700,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C18" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D18" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2705,13 +2714,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D19" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2719,13 +2728,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D20" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2733,13 +2742,13 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D21" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2747,13 +2756,13 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D22" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2761,13 +2770,13 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D23" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2775,13 +2784,13 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D24" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2789,13 +2798,13 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D25" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2803,13 +2812,13 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D26" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2817,13 +2826,13 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D27" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2831,13 +2840,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2845,13 +2854,13 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D29" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2859,13 +2868,13 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C30" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D30" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2873,13 +2882,13 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C31" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2887,13 +2896,13 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C32" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2901,13 +2910,13 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C33" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2915,13 +2924,13 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C34" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D34" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2929,13 +2938,13 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C35" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D35" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2943,13 +2952,13 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C36" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D36" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2957,13 +2966,13 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C37" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D37" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2971,13 +2980,13 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C38" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D38" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2985,13 +2994,13 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C39" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D39" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2999,13 +3008,13 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C40" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D40" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3013,13 +3022,13 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C41" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D41" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3027,13 +3036,13 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C42" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D42" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3041,13 +3050,13 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C43" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D43" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3055,13 +3064,13 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C44" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D44" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3069,13 +3078,13 @@
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C45" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D45" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3083,13 +3092,13 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C46" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D46" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3097,13 +3106,13 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C47" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D47" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3111,13 +3120,13 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C48" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D48" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3125,13 +3134,13 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C49" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D49" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3139,13 +3148,13 @@
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C50" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D50" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3153,13 +3162,13 @@
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C51" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D51" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3167,13 +3176,13 @@
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C52" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D52" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3181,13 +3190,13 @@
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C53" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D53" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3195,13 +3204,13 @@
         <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C54" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D54" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3209,13 +3218,13 @@
         <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C55" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D55" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3223,13 +3232,13 @@
         <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C56" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D56" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3237,13 +3246,13 @@
         <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C57" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D57" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3251,13 +3260,13 @@
         <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C58" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D58" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3265,13 +3274,13 @@
         <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C59" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D59" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3279,13 +3288,13 @@
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C60" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D60" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3293,13 +3302,13 @@
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C61" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D61" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3307,13 +3316,13 @@
         <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C62" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D62" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3321,13 +3330,13 @@
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C63" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D63" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3335,13 +3344,13 @@
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C64" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D64" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3349,13 +3358,13 @@
         <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C65" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D65" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3363,13 +3372,13 @@
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C66" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D66" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3377,13 +3386,13 @@
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C67" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D67" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3391,13 +3400,13 @@
         <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C68" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D68" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3405,13 +3414,13 @@
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C69" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D69" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3419,13 +3428,13 @@
         <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C70" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D70" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3433,13 +3442,13 @@
         <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C71" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D71" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3447,13 +3456,13 @@
         <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C72" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D72" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3461,13 +3470,13 @@
         <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C73" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D73" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3475,13 +3484,13 @@
         <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C74" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D74" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3489,13 +3498,13 @@
         <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D75" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3503,13 +3512,13 @@
         <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C76" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D76" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3517,13 +3526,13 @@
         <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C77" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D77" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3531,13 +3540,13 @@
         <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C78" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D78" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3545,13 +3554,13 @@
         <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C79" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D79" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3559,13 +3568,13 @@
         <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C80" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D80" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3573,13 +3582,13 @@
         <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C81" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D81" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3587,13 +3596,13 @@
         <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C82" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D82" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3601,13 +3610,13 @@
         <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C83" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D83" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3615,13 +3624,13 @@
         <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C84" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D84" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3629,13 +3638,13 @@
         <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C85" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D85" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3643,13 +3652,13 @@
         <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C86" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D86" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3657,13 +3666,13 @@
         <v>87</v>
       </c>
       <c r="B87" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C87" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D87" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3671,13 +3680,13 @@
         <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C88" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D88" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3685,13 +3694,13 @@
         <v>89</v>
       </c>
       <c r="B89" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C89" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D89" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3699,13 +3708,13 @@
         <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C90" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D90" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3713,13 +3722,13 @@
         <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C91" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D91" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3727,13 +3736,13 @@
         <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C92" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D92" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3741,13 +3750,13 @@
         <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C93" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D93" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3755,13 +3764,13 @@
         <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C94" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D94" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3769,13 +3778,13 @@
         <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C95" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D95" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3783,13 +3792,13 @@
         <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C96" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D96" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3797,13 +3806,13 @@
         <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C97" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D97" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3811,13 +3820,13 @@
         <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C98" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D98" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3825,13 +3834,13 @@
         <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C99" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D99" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3839,13 +3848,13 @@
         <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C100" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D100" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3853,13 +3862,13 @@
         <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C101" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D101" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3867,13 +3876,13 @@
         <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C102" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D102" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3881,13 +3890,13 @@
         <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C103" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D103" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3895,13 +3904,13 @@
         <v>104</v>
       </c>
       <c r="B104" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C104" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D104" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3909,13 +3918,13 @@
         <v>105</v>
       </c>
       <c r="B105" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C105" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D105" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3923,13 +3932,13 @@
         <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C106" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D106" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3937,13 +3946,13 @@
         <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C107" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D107" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3951,13 +3960,13 @@
         <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C108" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D108" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3965,13 +3974,13 @@
         <v>109</v>
       </c>
       <c r="B109" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C109" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D109" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3979,13 +3988,13 @@
         <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C110" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D110" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3993,13 +4002,13 @@
         <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C111" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D111" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4007,13 +4016,13 @@
         <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C112" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D112" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4021,13 +4030,13 @@
         <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C113" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D113" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4035,13 +4044,13 @@
         <v>114</v>
       </c>
       <c r="B114" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C114" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D114" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4049,13 +4058,13 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C115" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D115" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4063,13 +4072,13 @@
         <v>116</v>
       </c>
       <c r="B116" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C116" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D116" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4077,13 +4086,13 @@
         <v>117</v>
       </c>
       <c r="B117" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C117" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D117" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4091,13 +4100,13 @@
         <v>118</v>
       </c>
       <c r="B118" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C118" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D118" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4105,13 +4114,13 @@
         <v>119</v>
       </c>
       <c r="B119" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C119" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D119" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4119,13 +4128,13 @@
         <v>120</v>
       </c>
       <c r="B120" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C120" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D120" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4133,13 +4142,13 @@
         <v>121</v>
       </c>
       <c r="B121" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C121" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D121" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4147,13 +4156,13 @@
         <v>122</v>
       </c>
       <c r="B122" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C122" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D122" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4161,13 +4170,13 @@
         <v>123</v>
       </c>
       <c r="B123" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C123" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D123" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4175,13 +4184,13 @@
         <v>124</v>
       </c>
       <c r="B124" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C124" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D124" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4189,13 +4198,13 @@
         <v>125</v>
       </c>
       <c r="B125" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C125" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D125" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4203,13 +4212,13 @@
         <v>126</v>
       </c>
       <c r="B126" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C126" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D126" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4217,13 +4226,13 @@
         <v>127</v>
       </c>
       <c r="B127" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C127" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D127" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4231,13 +4240,13 @@
         <v>128</v>
       </c>
       <c r="B128" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C128" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D128" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4245,13 +4254,13 @@
         <v>129</v>
       </c>
       <c r="B129" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C129" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D129" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4259,13 +4268,13 @@
         <v>130</v>
       </c>
       <c r="B130" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C130" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D130" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4273,13 +4282,13 @@
         <v>131</v>
       </c>
       <c r="B131" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C131" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D131" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4287,13 +4296,13 @@
         <v>132</v>
       </c>
       <c r="B132" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C132" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D132" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4301,13 +4310,13 @@
         <v>133</v>
       </c>
       <c r="B133" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C133" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D133" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4315,13 +4324,13 @@
         <v>134</v>
       </c>
       <c r="B134" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C134" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D134" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4329,13 +4338,13 @@
         <v>135</v>
       </c>
       <c r="B135" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C135" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D135" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4343,13 +4352,13 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C136" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D136" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4357,13 +4366,13 @@
         <v>137</v>
       </c>
       <c r="B137" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C137" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D137" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4371,13 +4380,13 @@
         <v>138</v>
       </c>
       <c r="B138" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C138" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D138" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4385,13 +4394,13 @@
         <v>139</v>
       </c>
       <c r="B139" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C139" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D139" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4399,13 +4408,13 @@
         <v>140</v>
       </c>
       <c r="B140" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C140" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D140" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4413,13 +4422,13 @@
         <v>141</v>
       </c>
       <c r="B141" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C141" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D141" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4427,13 +4436,13 @@
         <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C142" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D142" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4441,13 +4450,13 @@
         <v>143</v>
       </c>
       <c r="B143" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C143" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D143" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4455,13 +4464,13 @@
         <v>144</v>
       </c>
       <c r="B144" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C144" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D144" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4469,13 +4478,13 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C145" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D145" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4483,13 +4492,13 @@
         <v>146</v>
       </c>
       <c r="B146" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C146" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D146" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4497,13 +4506,13 @@
         <v>147</v>
       </c>
       <c r="B147" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C147" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D147" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4511,13 +4520,13 @@
         <v>148</v>
       </c>
       <c r="B148" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C148" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D148" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4525,13 +4534,13 @@
         <v>149</v>
       </c>
       <c r="B149" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C149" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D149" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4539,13 +4548,13 @@
         <v>150</v>
       </c>
       <c r="B150" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C150" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D150" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4553,13 +4562,13 @@
         <v>151</v>
       </c>
       <c r="B151" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C151" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D151" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4567,13 +4576,13 @@
         <v>152</v>
       </c>
       <c r="B152" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C152" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D152" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4581,13 +4590,13 @@
         <v>153</v>
       </c>
       <c r="B153" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C153" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D153" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4595,13 +4604,13 @@
         <v>154</v>
       </c>
       <c r="B154" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C154" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D154" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4609,13 +4618,13 @@
         <v>155</v>
       </c>
       <c r="B155" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C155" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D155" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4623,13 +4632,13 @@
         <v>156</v>
       </c>
       <c r="B156" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C156" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D156" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4637,13 +4646,13 @@
         <v>157</v>
       </c>
       <c r="B157" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C157" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D157" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4651,13 +4660,13 @@
         <v>158</v>
       </c>
       <c r="B158" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C158" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D158" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4665,13 +4674,13 @@
         <v>159</v>
       </c>
       <c r="B159" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C159" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D159" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4679,13 +4688,13 @@
         <v>160</v>
       </c>
       <c r="B160" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C160" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D160" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4693,13 +4702,13 @@
         <v>161</v>
       </c>
       <c r="B161" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C161" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D161" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4707,13 +4716,13 @@
         <v>162</v>
       </c>
       <c r="B162" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C162" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D162" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4721,13 +4730,13 @@
         <v>163</v>
       </c>
       <c r="B163" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C163" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D163" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4735,13 +4744,13 @@
         <v>164</v>
       </c>
       <c r="B164" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C164" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D164" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4749,13 +4758,13 @@
         <v>165</v>
       </c>
       <c r="B165" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C165" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D165" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4763,13 +4772,13 @@
         <v>166</v>
       </c>
       <c r="B166" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C166" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D166" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4777,13 +4786,13 @@
         <v>167</v>
       </c>
       <c r="B167" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C167" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D167" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4791,13 +4800,13 @@
         <v>168</v>
       </c>
       <c r="B168" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C168" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D168" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4805,13 +4814,13 @@
         <v>169</v>
       </c>
       <c r="B169" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C169" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D169" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4819,13 +4828,13 @@
         <v>170</v>
       </c>
       <c r="B170" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C170" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D170" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4833,13 +4842,13 @@
         <v>171</v>
       </c>
       <c r="B171" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C171" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D171" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4847,13 +4856,13 @@
         <v>172</v>
       </c>
       <c r="B172" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C172" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D172" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4861,13 +4870,13 @@
         <v>173</v>
       </c>
       <c r="B173" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C173" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D173" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4875,13 +4884,13 @@
         <v>174</v>
       </c>
       <c r="B174" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C174" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D174" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4889,13 +4898,13 @@
         <v>175</v>
       </c>
       <c r="B175" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C175" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D175" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4903,13 +4912,13 @@
         <v>176</v>
       </c>
       <c r="B176" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C176" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D176" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4917,13 +4926,13 @@
         <v>177</v>
       </c>
       <c r="B177" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C177" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D177" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4931,13 +4940,13 @@
         <v>178</v>
       </c>
       <c r="B178" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C178" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D178" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4945,13 +4954,13 @@
         <v>179</v>
       </c>
       <c r="B179" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C179" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D179" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4959,13 +4968,13 @@
         <v>180</v>
       </c>
       <c r="B180" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C180" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D180" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4973,13 +4982,13 @@
         <v>181</v>
       </c>
       <c r="B181" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C181" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D181" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4987,13 +4996,13 @@
         <v>182</v>
       </c>
       <c r="B182" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C182" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D182" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5001,13 +5010,13 @@
         <v>183</v>
       </c>
       <c r="B183" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C183" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D183" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5015,13 +5024,13 @@
         <v>184</v>
       </c>
       <c r="B184" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C184" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D184" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5029,13 +5038,13 @@
         <v>185</v>
       </c>
       <c r="B185" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C185" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D185" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5043,13 +5052,13 @@
         <v>186</v>
       </c>
       <c r="B186" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C186" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D186" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5057,13 +5066,13 @@
         <v>187</v>
       </c>
       <c r="B187" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C187" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D187" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5071,13 +5080,13 @@
         <v>188</v>
       </c>
       <c r="B188" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C188" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D188" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5085,13 +5094,13 @@
         <v>189</v>
       </c>
       <c r="B189" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C189" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D189" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5099,13 +5108,13 @@
         <v>190</v>
       </c>
       <c r="B190" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C190" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D190" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5113,13 +5122,13 @@
         <v>191</v>
       </c>
       <c r="B191" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C191" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D191" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5127,13 +5136,13 @@
         <v>192</v>
       </c>
       <c r="B192" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C192" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D192" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5141,13 +5150,13 @@
         <v>193</v>
       </c>
       <c r="B193" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C193" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D193" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5155,13 +5164,13 @@
         <v>194</v>
       </c>
       <c r="B194" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C194" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D194" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5169,13 +5178,13 @@
         <v>195</v>
       </c>
       <c r="B195" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C195" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D195" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5183,13 +5192,13 @@
         <v>196</v>
       </c>
       <c r="B196" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C196" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D196" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5197,13 +5206,13 @@
         <v>197</v>
       </c>
       <c r="B197" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C197" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D197" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5211,13 +5220,13 @@
         <v>198</v>
       </c>
       <c r="B198" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C198" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D198" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5225,13 +5234,13 @@
         <v>199</v>
       </c>
       <c r="B199" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C199" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D199" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5239,13 +5248,13 @@
         <v>200</v>
       </c>
       <c r="B200" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C200" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D200" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5253,13 +5262,13 @@
         <v>201</v>
       </c>
       <c r="B201" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C201" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D201" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5267,13 +5276,13 @@
         <v>202</v>
       </c>
       <c r="B202" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C202" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D202" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5281,13 +5290,13 @@
         <v>203</v>
       </c>
       <c r="B203" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C203" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D203" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5295,13 +5304,13 @@
         <v>204</v>
       </c>
       <c r="B204" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C204" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D204" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5309,13 +5318,13 @@
         <v>205</v>
       </c>
       <c r="B205" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C205" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D205" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5323,13 +5332,13 @@
         <v>206</v>
       </c>
       <c r="B206" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C206" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D206" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5337,13 +5346,13 @@
         <v>207</v>
       </c>
       <c r="B207" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C207" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D207" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5351,13 +5360,13 @@
         <v>208</v>
       </c>
       <c r="B208" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C208" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D208" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5365,13 +5374,13 @@
         <v>209</v>
       </c>
       <c r="B209" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C209" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D209" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5379,13 +5388,13 @@
         <v>210</v>
       </c>
       <c r="B210" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C210" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D210" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5393,13 +5402,13 @@
         <v>211</v>
       </c>
       <c r="B211" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C211" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D211" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5407,13 +5416,13 @@
         <v>212</v>
       </c>
       <c r="B212" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C212" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D212" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5421,13 +5430,13 @@
         <v>213</v>
       </c>
       <c r="B213" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C213" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D213" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5435,13 +5444,13 @@
         <v>214</v>
       </c>
       <c r="B214" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C214" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D214" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5449,13 +5458,13 @@
         <v>215</v>
       </c>
       <c r="B215" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C215" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D215" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5463,13 +5472,13 @@
         <v>216</v>
       </c>
       <c r="B216" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C216" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D216" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5477,13 +5486,13 @@
         <v>217</v>
       </c>
       <c r="B217" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C217" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D217" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5491,13 +5500,13 @@
         <v>218</v>
       </c>
       <c r="B218" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C218" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D218" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5505,13 +5514,13 @@
         <v>219</v>
       </c>
       <c r="B219" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C219" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D219" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5519,13 +5528,13 @@
         <v>220</v>
       </c>
       <c r="B220" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C220" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D220" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5533,13 +5542,13 @@
         <v>221</v>
       </c>
       <c r="B221" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C221" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D221" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5547,13 +5556,13 @@
         <v>222</v>
       </c>
       <c r="B222" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C222" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D222" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5561,13 +5570,13 @@
         <v>223</v>
       </c>
       <c r="B223" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C223" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D223" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5575,13 +5584,13 @@
         <v>224</v>
       </c>
       <c r="B224" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C224" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D224" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5589,13 +5598,13 @@
         <v>225</v>
       </c>
       <c r="B225" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C225" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D225" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5603,13 +5612,13 @@
         <v>226</v>
       </c>
       <c r="B226" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C226" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D226" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5617,13 +5626,13 @@
         <v>227</v>
       </c>
       <c r="B227" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C227" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D227" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5631,13 +5640,13 @@
         <v>228</v>
       </c>
       <c r="B228" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C228" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D228" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5645,13 +5654,13 @@
         <v>229</v>
       </c>
       <c r="B229" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C229" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D229" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5659,13 +5668,13 @@
         <v>230</v>
       </c>
       <c r="B230" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C230" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D230" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5673,13 +5682,13 @@
         <v>231</v>
       </c>
       <c r="B231" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C231" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D231" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5687,13 +5696,13 @@
         <v>232</v>
       </c>
       <c r="B232" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C232" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D232" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5707,7 +5716,7 @@
         <v>233</v>
       </c>
       <c r="D233" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5721,7 +5730,7 @@
         <v>234</v>
       </c>
       <c r="D234" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5729,13 +5738,27 @@
         <v>235</v>
       </c>
       <c r="B235" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C235" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D235" t="s">
-        <v>699</v>
+        <v>701</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" t="s">
+        <v>236</v>
+      </c>
+      <c r="B236" t="s">
+        <v>467</v>
+      </c>
+      <c r="C236" t="s">
+        <v>467</v>
+      </c>
+      <c r="D236" t="s">
+        <v>702</v>
       </c>
     </row>
   </sheetData>

--- a/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
+++ b/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="706">
   <si>
     <t>Tên Siêu thị</t>
   </si>
@@ -727,6 +727,9 @@
     <t>KFM_HCM_PNH - Hoa Sứ</t>
   </si>
   <si>
+    <t>KFM_HCM_Q12 - S.06 Chung Cư Phú Cường Home</t>
+  </si>
+  <si>
     <t>A101</t>
   </si>
   <si>
@@ -1420,6 +1423,9 @@
     <t>A266</t>
   </si>
   <si>
+    <t>A254</t>
+  </si>
+  <si>
     <t>-4970846623</t>
   </si>
   <si>
@@ -2123,6 +2129,9 @@
   </si>
   <si>
     <t>-1004376355185</t>
+  </si>
+  <si>
+    <t>-1003932058795</t>
   </si>
 </sst>
 </file>
@@ -2454,7 +2463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D236"/>
+  <dimension ref="A1:D237"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2476,13 +2485,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2490,13 +2499,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2504,13 +2513,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D4" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2518,13 +2527,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D5" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2532,13 +2541,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D6" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2546,13 +2555,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D7" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2560,13 +2569,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D8" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2574,13 +2583,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D9" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2588,13 +2597,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D10" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2602,13 +2611,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D11" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2616,13 +2625,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D12" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2630,13 +2639,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D13" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2644,13 +2653,13 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D14" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2658,13 +2667,13 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2672,13 +2681,13 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D16" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2686,13 +2695,13 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D17" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2700,13 +2709,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D18" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2714,13 +2723,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D19" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2728,13 +2737,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D20" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2742,13 +2751,13 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D21" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2756,13 +2765,13 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D22" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2770,13 +2779,13 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D23" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2784,13 +2793,13 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D24" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2798,13 +2807,13 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2812,13 +2821,13 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D26" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2826,13 +2835,13 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2840,13 +2849,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D28" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2854,13 +2863,13 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C29" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D29" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2868,13 +2877,13 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D30" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2882,13 +2891,13 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C31" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2896,13 +2905,13 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C32" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D32" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2910,13 +2919,13 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D33" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2924,13 +2933,13 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C34" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D34" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2938,13 +2947,13 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C35" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D35" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2952,13 +2961,13 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C36" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D36" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2966,13 +2975,13 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C37" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D37" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2980,13 +2989,13 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C38" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D38" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2994,13 +3003,13 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C39" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D39" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3008,13 +3017,13 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C40" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D40" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3022,13 +3031,13 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C41" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D41" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3036,13 +3045,13 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C42" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D42" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3050,13 +3059,13 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C43" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D43" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3064,13 +3073,13 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C44" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D44" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3078,13 +3087,13 @@
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C45" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D45" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3092,13 +3101,13 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C46" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D46" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3106,13 +3115,13 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C47" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D47" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3120,13 +3129,13 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C48" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D48" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3134,13 +3143,13 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C49" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D49" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3148,13 +3157,13 @@
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C50" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D50" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3162,13 +3171,13 @@
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C51" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D51" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3176,13 +3185,13 @@
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C52" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D52" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3190,13 +3199,13 @@
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C53" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D53" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3204,13 +3213,13 @@
         <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C54" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D54" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3218,13 +3227,13 @@
         <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C55" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D55" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3232,13 +3241,13 @@
         <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C56" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D56" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3246,13 +3255,13 @@
         <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C57" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D57" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3260,13 +3269,13 @@
         <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C58" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D58" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3274,13 +3283,13 @@
         <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C59" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D59" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3288,13 +3297,13 @@
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C60" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D60" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3302,13 +3311,13 @@
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C61" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D61" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3316,13 +3325,13 @@
         <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C62" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D62" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3330,13 +3339,13 @@
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C63" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D63" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3344,13 +3353,13 @@
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C64" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D64" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3358,13 +3367,13 @@
         <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C65" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D65" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3372,13 +3381,13 @@
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C66" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D66" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3386,13 +3395,13 @@
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C67" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D67" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3400,13 +3409,13 @@
         <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C68" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D68" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3414,13 +3423,13 @@
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C69" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D69" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3428,13 +3437,13 @@
         <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C70" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D70" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3442,13 +3451,13 @@
         <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C71" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D71" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3456,13 +3465,13 @@
         <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C72" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D72" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3470,13 +3479,13 @@
         <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C73" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D73" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3484,13 +3493,13 @@
         <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C74" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D74" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3498,13 +3507,13 @@
         <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C75" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D75" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3512,13 +3521,13 @@
         <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C76" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D76" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3526,13 +3535,13 @@
         <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C77" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D77" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3540,13 +3549,13 @@
         <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C78" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D78" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3554,13 +3563,13 @@
         <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C79" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D79" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3568,13 +3577,13 @@
         <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C80" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D80" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3582,13 +3591,13 @@
         <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C81" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D81" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3596,13 +3605,13 @@
         <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C82" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D82" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3610,13 +3619,13 @@
         <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C83" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D83" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3624,13 +3633,13 @@
         <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C84" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D84" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3638,13 +3647,13 @@
         <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C85" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D85" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3652,13 +3661,13 @@
         <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C86" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D86" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3666,13 +3675,13 @@
         <v>87</v>
       </c>
       <c r="B87" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C87" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D87" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3680,13 +3689,13 @@
         <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C88" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D88" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3694,13 +3703,13 @@
         <v>89</v>
       </c>
       <c r="B89" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C89" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D89" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3708,13 +3717,13 @@
         <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C90" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D90" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3722,13 +3731,13 @@
         <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C91" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D91" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3736,13 +3745,13 @@
         <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C92" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D92" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3750,13 +3759,13 @@
         <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C93" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D93" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3764,13 +3773,13 @@
         <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C94" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D94" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3778,13 +3787,13 @@
         <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C95" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D95" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3792,13 +3801,13 @@
         <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C96" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D96" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3806,13 +3815,13 @@
         <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C97" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D97" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3820,13 +3829,13 @@
         <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C98" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D98" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3834,13 +3843,13 @@
         <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C99" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D99" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3848,13 +3857,13 @@
         <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C100" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D100" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3862,13 +3871,13 @@
         <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C101" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D101" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3876,13 +3885,13 @@
         <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C102" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D102" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3890,13 +3899,13 @@
         <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C103" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D103" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3904,13 +3913,13 @@
         <v>104</v>
       </c>
       <c r="B104" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C104" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D104" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3918,13 +3927,13 @@
         <v>105</v>
       </c>
       <c r="B105" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C105" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D105" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3932,13 +3941,13 @@
         <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C106" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D106" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3946,13 +3955,13 @@
         <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C107" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D107" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3960,13 +3969,13 @@
         <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C108" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D108" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3974,13 +3983,13 @@
         <v>109</v>
       </c>
       <c r="B109" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C109" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D109" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3988,13 +3997,13 @@
         <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C110" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D110" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4002,13 +4011,13 @@
         <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C111" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D111" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4016,13 +4025,13 @@
         <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C112" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D112" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4030,13 +4039,13 @@
         <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C113" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D113" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4044,13 +4053,13 @@
         <v>114</v>
       </c>
       <c r="B114" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C114" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D114" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4058,13 +4067,13 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C115" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D115" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4072,13 +4081,13 @@
         <v>116</v>
       </c>
       <c r="B116" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C116" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D116" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4086,13 +4095,13 @@
         <v>117</v>
       </c>
       <c r="B117" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C117" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D117" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4100,13 +4109,13 @@
         <v>118</v>
       </c>
       <c r="B118" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C118" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D118" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4114,13 +4123,13 @@
         <v>119</v>
       </c>
       <c r="B119" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C119" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D119" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4128,13 +4137,13 @@
         <v>120</v>
       </c>
       <c r="B120" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C120" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D120" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4142,13 +4151,13 @@
         <v>121</v>
       </c>
       <c r="B121" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C121" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D121" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4156,13 +4165,13 @@
         <v>122</v>
       </c>
       <c r="B122" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C122" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D122" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4170,13 +4179,13 @@
         <v>123</v>
       </c>
       <c r="B123" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C123" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D123" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4184,13 +4193,13 @@
         <v>124</v>
       </c>
       <c r="B124" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C124" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D124" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4198,13 +4207,13 @@
         <v>125</v>
       </c>
       <c r="B125" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C125" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D125" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4212,13 +4221,13 @@
         <v>126</v>
       </c>
       <c r="B126" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C126" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D126" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4226,13 +4235,13 @@
         <v>127</v>
       </c>
       <c r="B127" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C127" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D127" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4240,13 +4249,13 @@
         <v>128</v>
       </c>
       <c r="B128" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C128" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D128" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4254,13 +4263,13 @@
         <v>129</v>
       </c>
       <c r="B129" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C129" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D129" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4268,13 +4277,13 @@
         <v>130</v>
       </c>
       <c r="B130" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C130" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D130" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4282,13 +4291,13 @@
         <v>131</v>
       </c>
       <c r="B131" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C131" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D131" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4296,13 +4305,13 @@
         <v>132</v>
       </c>
       <c r="B132" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C132" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D132" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4310,13 +4319,13 @@
         <v>133</v>
       </c>
       <c r="B133" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C133" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D133" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4324,13 +4333,13 @@
         <v>134</v>
       </c>
       <c r="B134" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C134" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D134" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4338,13 +4347,13 @@
         <v>135</v>
       </c>
       <c r="B135" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C135" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D135" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4352,13 +4361,13 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C136" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D136" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4366,13 +4375,13 @@
         <v>137</v>
       </c>
       <c r="B137" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C137" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D137" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4380,13 +4389,13 @@
         <v>138</v>
       </c>
       <c r="B138" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C138" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D138" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4394,13 +4403,13 @@
         <v>139</v>
       </c>
       <c r="B139" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C139" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D139" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4408,13 +4417,13 @@
         <v>140</v>
       </c>
       <c r="B140" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C140" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D140" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4422,13 +4431,13 @@
         <v>141</v>
       </c>
       <c r="B141" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C141" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D141" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4436,13 +4445,13 @@
         <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C142" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D142" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4450,13 +4459,13 @@
         <v>143</v>
       </c>
       <c r="B143" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C143" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D143" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4464,13 +4473,13 @@
         <v>144</v>
       </c>
       <c r="B144" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C144" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D144" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4478,13 +4487,13 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C145" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D145" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4492,13 +4501,13 @@
         <v>146</v>
       </c>
       <c r="B146" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C146" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D146" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4506,13 +4515,13 @@
         <v>147</v>
       </c>
       <c r="B147" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C147" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D147" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4520,13 +4529,13 @@
         <v>148</v>
       </c>
       <c r="B148" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C148" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D148" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4534,13 +4543,13 @@
         <v>149</v>
       </c>
       <c r="B149" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C149" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D149" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4548,13 +4557,13 @@
         <v>150</v>
       </c>
       <c r="B150" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C150" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D150" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4562,13 +4571,13 @@
         <v>151</v>
       </c>
       <c r="B151" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C151" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D151" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4576,13 +4585,13 @@
         <v>152</v>
       </c>
       <c r="B152" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C152" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D152" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4590,13 +4599,13 @@
         <v>153</v>
       </c>
       <c r="B153" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C153" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D153" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4604,13 +4613,13 @@
         <v>154</v>
       </c>
       <c r="B154" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C154" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D154" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4618,13 +4627,13 @@
         <v>155</v>
       </c>
       <c r="B155" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C155" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D155" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4632,13 +4641,13 @@
         <v>156</v>
       </c>
       <c r="B156" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C156" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D156" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4646,13 +4655,13 @@
         <v>157</v>
       </c>
       <c r="B157" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C157" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D157" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4660,13 +4669,13 @@
         <v>158</v>
       </c>
       <c r="B158" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C158" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D158" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4674,13 +4683,13 @@
         <v>159</v>
       </c>
       <c r="B159" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C159" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D159" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4688,13 +4697,13 @@
         <v>160</v>
       </c>
       <c r="B160" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C160" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D160" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4702,13 +4711,13 @@
         <v>161</v>
       </c>
       <c r="B161" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C161" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D161" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4716,13 +4725,13 @@
         <v>162</v>
       </c>
       <c r="B162" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C162" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D162" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4730,13 +4739,13 @@
         <v>163</v>
       </c>
       <c r="B163" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C163" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D163" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4744,13 +4753,13 @@
         <v>164</v>
       </c>
       <c r="B164" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C164" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D164" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4758,13 +4767,13 @@
         <v>165</v>
       </c>
       <c r="B165" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C165" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D165" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4772,13 +4781,13 @@
         <v>166</v>
       </c>
       <c r="B166" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C166" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D166" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4786,13 +4795,13 @@
         <v>167</v>
       </c>
       <c r="B167" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C167" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D167" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4800,13 +4809,13 @@
         <v>168</v>
       </c>
       <c r="B168" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C168" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D168" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4814,13 +4823,13 @@
         <v>169</v>
       </c>
       <c r="B169" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C169" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D169" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4828,13 +4837,13 @@
         <v>170</v>
       </c>
       <c r="B170" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C170" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D170" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4842,13 +4851,13 @@
         <v>171</v>
       </c>
       <c r="B171" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C171" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D171" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4856,13 +4865,13 @@
         <v>172</v>
       </c>
       <c r="B172" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C172" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D172" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4870,13 +4879,13 @@
         <v>173</v>
       </c>
       <c r="B173" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C173" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D173" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4884,13 +4893,13 @@
         <v>174</v>
       </c>
       <c r="B174" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C174" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D174" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4898,13 +4907,13 @@
         <v>175</v>
       </c>
       <c r="B175" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C175" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D175" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4912,13 +4921,13 @@
         <v>176</v>
       </c>
       <c r="B176" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C176" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D176" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4926,13 +4935,13 @@
         <v>177</v>
       </c>
       <c r="B177" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C177" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D177" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4940,13 +4949,13 @@
         <v>178</v>
       </c>
       <c r="B178" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C178" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D178" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4954,13 +4963,13 @@
         <v>179</v>
       </c>
       <c r="B179" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C179" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D179" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4968,13 +4977,13 @@
         <v>180</v>
       </c>
       <c r="B180" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C180" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D180" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4982,13 +4991,13 @@
         <v>181</v>
       </c>
       <c r="B181" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C181" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D181" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4996,13 +5005,13 @@
         <v>182</v>
       </c>
       <c r="B182" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C182" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D182" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5010,13 +5019,13 @@
         <v>183</v>
       </c>
       <c r="B183" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C183" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D183" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5024,13 +5033,13 @@
         <v>184</v>
       </c>
       <c r="B184" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C184" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D184" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5038,13 +5047,13 @@
         <v>185</v>
       </c>
       <c r="B185" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C185" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D185" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5052,13 +5061,13 @@
         <v>186</v>
       </c>
       <c r="B186" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C186" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D186" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5066,13 +5075,13 @@
         <v>187</v>
       </c>
       <c r="B187" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C187" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D187" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5080,13 +5089,13 @@
         <v>188</v>
       </c>
       <c r="B188" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C188" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D188" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5094,13 +5103,13 @@
         <v>189</v>
       </c>
       <c r="B189" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C189" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D189" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5108,13 +5117,13 @@
         <v>190</v>
       </c>
       <c r="B190" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C190" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D190" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5122,13 +5131,13 @@
         <v>191</v>
       </c>
       <c r="B191" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C191" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D191" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5136,13 +5145,13 @@
         <v>192</v>
       </c>
       <c r="B192" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C192" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D192" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5150,13 +5159,13 @@
         <v>193</v>
       </c>
       <c r="B193" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C193" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D193" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5164,13 +5173,13 @@
         <v>194</v>
       </c>
       <c r="B194" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C194" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D194" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5178,13 +5187,13 @@
         <v>195</v>
       </c>
       <c r="B195" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C195" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D195" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5192,13 +5201,13 @@
         <v>196</v>
       </c>
       <c r="B196" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C196" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D196" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5206,13 +5215,13 @@
         <v>197</v>
       </c>
       <c r="B197" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C197" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D197" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5220,13 +5229,13 @@
         <v>198</v>
       </c>
       <c r="B198" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C198" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D198" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5234,13 +5243,13 @@
         <v>199</v>
       </c>
       <c r="B199" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C199" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D199" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5248,13 +5257,13 @@
         <v>200</v>
       </c>
       <c r="B200" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C200" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D200" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5262,13 +5271,13 @@
         <v>201</v>
       </c>
       <c r="B201" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C201" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D201" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5276,13 +5285,13 @@
         <v>202</v>
       </c>
       <c r="B202" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C202" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D202" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5290,13 +5299,13 @@
         <v>203</v>
       </c>
       <c r="B203" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C203" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D203" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5304,13 +5313,13 @@
         <v>204</v>
       </c>
       <c r="B204" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C204" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D204" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5318,13 +5327,13 @@
         <v>205</v>
       </c>
       <c r="B205" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C205" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D205" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5332,13 +5341,13 @@
         <v>206</v>
       </c>
       <c r="B206" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C206" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D206" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5346,13 +5355,13 @@
         <v>207</v>
       </c>
       <c r="B207" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C207" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D207" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5360,13 +5369,13 @@
         <v>208</v>
       </c>
       <c r="B208" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C208" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D208" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5374,13 +5383,13 @@
         <v>209</v>
       </c>
       <c r="B209" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C209" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D209" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5388,13 +5397,13 @@
         <v>210</v>
       </c>
       <c r="B210" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C210" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D210" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5402,13 +5411,13 @@
         <v>211</v>
       </c>
       <c r="B211" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C211" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D211" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5416,13 +5425,13 @@
         <v>212</v>
       </c>
       <c r="B212" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C212" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D212" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5430,13 +5439,13 @@
         <v>213</v>
       </c>
       <c r="B213" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C213" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D213" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5444,13 +5453,13 @@
         <v>214</v>
       </c>
       <c r="B214" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C214" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D214" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5458,13 +5467,13 @@
         <v>215</v>
       </c>
       <c r="B215" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C215" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D215" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5472,13 +5481,13 @@
         <v>216</v>
       </c>
       <c r="B216" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C216" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D216" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5486,13 +5495,13 @@
         <v>217</v>
       </c>
       <c r="B217" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C217" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D217" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5500,13 +5509,13 @@
         <v>218</v>
       </c>
       <c r="B218" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C218" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D218" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5514,13 +5523,13 @@
         <v>219</v>
       </c>
       <c r="B219" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C219" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D219" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5528,13 +5537,13 @@
         <v>220</v>
       </c>
       <c r="B220" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C220" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D220" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5542,13 +5551,13 @@
         <v>221</v>
       </c>
       <c r="B221" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C221" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D221" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5556,13 +5565,13 @@
         <v>222</v>
       </c>
       <c r="B222" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C222" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D222" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5570,13 +5579,13 @@
         <v>223</v>
       </c>
       <c r="B223" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C223" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D223" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5584,13 +5593,13 @@
         <v>224</v>
       </c>
       <c r="B224" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C224" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D224" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5598,13 +5607,13 @@
         <v>225</v>
       </c>
       <c r="B225" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C225" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D225" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5612,13 +5621,13 @@
         <v>226</v>
       </c>
       <c r="B226" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C226" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D226" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5626,13 +5635,13 @@
         <v>227</v>
       </c>
       <c r="B227" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C227" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D227" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5640,13 +5649,13 @@
         <v>228</v>
       </c>
       <c r="B228" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C228" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D228" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5654,13 +5663,13 @@
         <v>229</v>
       </c>
       <c r="B229" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C229" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D229" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5668,13 +5677,13 @@
         <v>230</v>
       </c>
       <c r="B230" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C230" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D230" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5682,13 +5691,13 @@
         <v>231</v>
       </c>
       <c r="B231" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C231" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D231" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5696,13 +5705,13 @@
         <v>232</v>
       </c>
       <c r="B232" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C232" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D232" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5716,7 +5725,7 @@
         <v>233</v>
       </c>
       <c r="D233" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5730,7 +5739,7 @@
         <v>234</v>
       </c>
       <c r="D234" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5738,13 +5747,13 @@
         <v>235</v>
       </c>
       <c r="B235" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C235" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D235" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5752,13 +5761,27 @@
         <v>236</v>
       </c>
       <c r="B236" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C236" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D236" t="s">
-        <v>702</v>
+        <v>704</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" t="s">
+        <v>237</v>
+      </c>
+      <c r="B237" t="s">
+        <v>469</v>
+      </c>
+      <c r="C237" t="s">
+        <v>469</v>
+      </c>
+      <c r="D237" t="s">
+        <v>705</v>
       </c>
     </row>
   </sheetData>

--- a/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
+++ b/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="709">
   <si>
     <t>Tên Siêu thị</t>
   </si>
@@ -730,6 +730,9 @@
     <t>KFM_HCM_Q12 - S.06 Chung Cư Phú Cường Home</t>
   </si>
   <si>
+    <t>KFM_BDU_DAN - R01.14 Block A2 Charm Ruby</t>
+  </si>
+  <si>
     <t>A101</t>
   </si>
   <si>
@@ -1426,6 +1429,9 @@
     <t>A254</t>
   </si>
   <si>
+    <t>A262</t>
+  </si>
+  <si>
     <t>-4970846623</t>
   </si>
   <si>
@@ -2132,6 +2138,9 @@
   </si>
   <si>
     <t>-1003932058795</t>
+  </si>
+  <si>
+    <t>-1004438420846</t>
   </si>
 </sst>
 </file>
@@ -2463,7 +2472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D237"/>
+  <dimension ref="A1:D238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2485,13 +2494,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2499,13 +2508,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2513,13 +2522,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2527,13 +2536,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D5" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2541,13 +2550,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D6" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2555,13 +2564,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D7" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2569,13 +2578,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D8" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2583,13 +2592,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D9" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2597,13 +2606,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D10" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2611,13 +2620,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D11" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2625,13 +2634,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D12" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2639,13 +2648,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D13" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2653,13 +2662,13 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D14" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2667,13 +2676,13 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D15" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2681,13 +2690,13 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D16" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2695,13 +2704,13 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D17" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2709,13 +2718,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D18" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2723,13 +2732,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D19" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2737,13 +2746,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C20" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D20" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2751,13 +2760,13 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D21" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2765,13 +2774,13 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D22" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2779,13 +2788,13 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C23" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D23" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2793,13 +2802,13 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2807,13 +2816,13 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D25" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2821,13 +2830,13 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2835,13 +2844,13 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D27" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2849,13 +2858,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D28" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2863,13 +2872,13 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D29" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2877,13 +2886,13 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C30" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D30" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2891,13 +2900,13 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C31" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D31" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2905,13 +2914,13 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D32" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2919,13 +2928,13 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D33" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2933,13 +2942,13 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C34" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D34" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2947,13 +2956,13 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C35" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D35" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2961,13 +2970,13 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D36" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2975,13 +2984,13 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C37" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D37" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2989,13 +2998,13 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C38" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D38" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3003,13 +3012,13 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C39" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D39" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3017,13 +3026,13 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C40" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D40" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3031,13 +3040,13 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C41" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D41" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3045,13 +3054,13 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C42" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D42" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3059,13 +3068,13 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C43" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D43" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3073,13 +3082,13 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C44" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D44" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3087,13 +3096,13 @@
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C45" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D45" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3101,13 +3110,13 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C46" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D46" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3115,13 +3124,13 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C47" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D47" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3129,13 +3138,13 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C48" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D48" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3143,13 +3152,13 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C49" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D49" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3157,13 +3166,13 @@
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D50" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3171,13 +3180,13 @@
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C51" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D51" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3185,13 +3194,13 @@
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C52" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D52" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3199,13 +3208,13 @@
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C53" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D53" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3213,13 +3222,13 @@
         <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C54" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D54" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3227,13 +3236,13 @@
         <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C55" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D55" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3241,13 +3250,13 @@
         <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C56" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D56" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3255,13 +3264,13 @@
         <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C57" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D57" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3269,13 +3278,13 @@
         <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C58" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D58" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3283,13 +3292,13 @@
         <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C59" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D59" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3297,13 +3306,13 @@
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C60" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D60" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3311,13 +3320,13 @@
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C61" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D61" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3325,13 +3334,13 @@
         <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C62" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D62" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3339,13 +3348,13 @@
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C63" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D63" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3353,13 +3362,13 @@
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C64" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D64" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3367,13 +3376,13 @@
         <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C65" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D65" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3381,13 +3390,13 @@
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C66" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D66" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3395,13 +3404,13 @@
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C67" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D67" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3409,13 +3418,13 @@
         <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C68" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D68" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3423,13 +3432,13 @@
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C69" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D69" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3437,13 +3446,13 @@
         <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C70" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D70" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3451,13 +3460,13 @@
         <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C71" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D71" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3465,13 +3474,13 @@
         <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C72" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D72" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3479,13 +3488,13 @@
         <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C73" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D73" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3493,13 +3502,13 @@
         <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C74" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D74" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3507,13 +3516,13 @@
         <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C75" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D75" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3521,13 +3530,13 @@
         <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C76" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D76" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3535,13 +3544,13 @@
         <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C77" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D77" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3549,13 +3558,13 @@
         <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C78" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D78" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3563,13 +3572,13 @@
         <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C79" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D79" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3577,13 +3586,13 @@
         <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C80" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D80" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3591,13 +3600,13 @@
         <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C81" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D81" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3605,13 +3614,13 @@
         <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C82" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D82" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3619,13 +3628,13 @@
         <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C83" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D83" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3633,13 +3642,13 @@
         <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C84" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D84" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3647,13 +3656,13 @@
         <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C85" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D85" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3661,13 +3670,13 @@
         <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C86" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D86" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3675,13 +3684,13 @@
         <v>87</v>
       </c>
       <c r="B87" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C87" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D87" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3689,13 +3698,13 @@
         <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C88" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D88" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3703,13 +3712,13 @@
         <v>89</v>
       </c>
       <c r="B89" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C89" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D89" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3717,13 +3726,13 @@
         <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C90" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D90" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3731,13 +3740,13 @@
         <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C91" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D91" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3745,13 +3754,13 @@
         <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C92" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D92" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3759,13 +3768,13 @@
         <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C93" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D93" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3773,13 +3782,13 @@
         <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C94" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D94" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3787,13 +3796,13 @@
         <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C95" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D95" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3801,13 +3810,13 @@
         <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C96" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D96" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3815,13 +3824,13 @@
         <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C97" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D97" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3829,13 +3838,13 @@
         <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C98" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D98" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3843,13 +3852,13 @@
         <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C99" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D99" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3857,13 +3866,13 @@
         <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C100" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D100" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3871,13 +3880,13 @@
         <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C101" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D101" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3885,13 +3894,13 @@
         <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C102" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D102" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3899,13 +3908,13 @@
         <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C103" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D103" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3913,13 +3922,13 @@
         <v>104</v>
       </c>
       <c r="B104" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C104" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D104" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3927,13 +3936,13 @@
         <v>105</v>
       </c>
       <c r="B105" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C105" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D105" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3941,13 +3950,13 @@
         <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C106" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D106" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3955,13 +3964,13 @@
         <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C107" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D107" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3969,13 +3978,13 @@
         <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C108" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D108" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3983,13 +3992,13 @@
         <v>109</v>
       </c>
       <c r="B109" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C109" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D109" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3997,13 +4006,13 @@
         <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C110" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D110" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4011,13 +4020,13 @@
         <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C111" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D111" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4025,13 +4034,13 @@
         <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C112" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D112" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4039,13 +4048,13 @@
         <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C113" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D113" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4053,13 +4062,13 @@
         <v>114</v>
       </c>
       <c r="B114" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C114" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D114" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4067,13 +4076,13 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C115" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D115" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4081,13 +4090,13 @@
         <v>116</v>
       </c>
       <c r="B116" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C116" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D116" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4095,13 +4104,13 @@
         <v>117</v>
       </c>
       <c r="B117" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C117" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D117" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4109,13 +4118,13 @@
         <v>118</v>
       </c>
       <c r="B118" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C118" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D118" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4123,13 +4132,13 @@
         <v>119</v>
       </c>
       <c r="B119" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C119" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D119" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4137,13 +4146,13 @@
         <v>120</v>
       </c>
       <c r="B120" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C120" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D120" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4151,13 +4160,13 @@
         <v>121</v>
       </c>
       <c r="B121" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C121" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D121" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4165,13 +4174,13 @@
         <v>122</v>
       </c>
       <c r="B122" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C122" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D122" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4179,13 +4188,13 @@
         <v>123</v>
       </c>
       <c r="B123" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C123" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D123" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4193,13 +4202,13 @@
         <v>124</v>
       </c>
       <c r="B124" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C124" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D124" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4207,13 +4216,13 @@
         <v>125</v>
       </c>
       <c r="B125" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C125" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D125" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4221,13 +4230,13 @@
         <v>126</v>
       </c>
       <c r="B126" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C126" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D126" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4235,13 +4244,13 @@
         <v>127</v>
       </c>
       <c r="B127" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C127" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D127" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4249,13 +4258,13 @@
         <v>128</v>
       </c>
       <c r="B128" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C128" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D128" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4263,13 +4272,13 @@
         <v>129</v>
       </c>
       <c r="B129" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C129" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D129" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4277,13 +4286,13 @@
         <v>130</v>
       </c>
       <c r="B130" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C130" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D130" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4291,13 +4300,13 @@
         <v>131</v>
       </c>
       <c r="B131" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C131" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D131" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4305,13 +4314,13 @@
         <v>132</v>
       </c>
       <c r="B132" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C132" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D132" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4319,13 +4328,13 @@
         <v>133</v>
       </c>
       <c r="B133" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C133" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D133" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4333,13 +4342,13 @@
         <v>134</v>
       </c>
       <c r="B134" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C134" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D134" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4347,13 +4356,13 @@
         <v>135</v>
       </c>
       <c r="B135" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C135" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D135" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4361,13 +4370,13 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C136" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D136" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4375,13 +4384,13 @@
         <v>137</v>
       </c>
       <c r="B137" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C137" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D137" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4389,13 +4398,13 @@
         <v>138</v>
       </c>
       <c r="B138" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C138" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D138" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4403,13 +4412,13 @@
         <v>139</v>
       </c>
       <c r="B139" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C139" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D139" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4417,13 +4426,13 @@
         <v>140</v>
       </c>
       <c r="B140" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C140" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D140" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4431,13 +4440,13 @@
         <v>141</v>
       </c>
       <c r="B141" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C141" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D141" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4445,13 +4454,13 @@
         <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C142" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D142" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4459,13 +4468,13 @@
         <v>143</v>
       </c>
       <c r="B143" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C143" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D143" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4473,13 +4482,13 @@
         <v>144</v>
       </c>
       <c r="B144" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C144" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D144" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4487,13 +4496,13 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C145" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D145" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4501,13 +4510,13 @@
         <v>146</v>
       </c>
       <c r="B146" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C146" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D146" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4515,13 +4524,13 @@
         <v>147</v>
       </c>
       <c r="B147" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C147" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D147" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4529,13 +4538,13 @@
         <v>148</v>
       </c>
       <c r="B148" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C148" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D148" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4543,13 +4552,13 @@
         <v>149</v>
       </c>
       <c r="B149" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C149" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D149" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4557,13 +4566,13 @@
         <v>150</v>
       </c>
       <c r="B150" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C150" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D150" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4571,13 +4580,13 @@
         <v>151</v>
       </c>
       <c r="B151" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C151" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D151" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4585,13 +4594,13 @@
         <v>152</v>
       </c>
       <c r="B152" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C152" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D152" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4599,13 +4608,13 @@
         <v>153</v>
       </c>
       <c r="B153" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C153" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D153" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4613,13 +4622,13 @@
         <v>154</v>
       </c>
       <c r="B154" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C154" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D154" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4627,13 +4636,13 @@
         <v>155</v>
       </c>
       <c r="B155" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C155" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D155" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4641,13 +4650,13 @@
         <v>156</v>
       </c>
       <c r="B156" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C156" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D156" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4655,13 +4664,13 @@
         <v>157</v>
       </c>
       <c r="B157" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C157" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D157" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4669,13 +4678,13 @@
         <v>158</v>
       </c>
       <c r="B158" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C158" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D158" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4683,13 +4692,13 @@
         <v>159</v>
       </c>
       <c r="B159" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C159" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D159" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4697,13 +4706,13 @@
         <v>160</v>
       </c>
       <c r="B160" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C160" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D160" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4711,13 +4720,13 @@
         <v>161</v>
       </c>
       <c r="B161" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C161" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D161" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4725,13 +4734,13 @@
         <v>162</v>
       </c>
       <c r="B162" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C162" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D162" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4739,13 +4748,13 @@
         <v>163</v>
       </c>
       <c r="B163" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C163" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D163" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4753,13 +4762,13 @@
         <v>164</v>
       </c>
       <c r="B164" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C164" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D164" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4767,13 +4776,13 @@
         <v>165</v>
       </c>
       <c r="B165" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C165" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D165" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4781,13 +4790,13 @@
         <v>166</v>
       </c>
       <c r="B166" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C166" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D166" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4795,13 +4804,13 @@
         <v>167</v>
       </c>
       <c r="B167" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C167" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D167" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4809,13 +4818,13 @@
         <v>168</v>
       </c>
       <c r="B168" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C168" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D168" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4823,13 +4832,13 @@
         <v>169</v>
       </c>
       <c r="B169" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C169" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D169" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4837,13 +4846,13 @@
         <v>170</v>
       </c>
       <c r="B170" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C170" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D170" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4851,13 +4860,13 @@
         <v>171</v>
       </c>
       <c r="B171" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C171" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D171" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4865,13 +4874,13 @@
         <v>172</v>
       </c>
       <c r="B172" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C172" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D172" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4879,13 +4888,13 @@
         <v>173</v>
       </c>
       <c r="B173" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C173" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D173" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4893,13 +4902,13 @@
         <v>174</v>
       </c>
       <c r="B174" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C174" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D174" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4907,13 +4916,13 @@
         <v>175</v>
       </c>
       <c r="B175" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C175" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D175" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4921,13 +4930,13 @@
         <v>176</v>
       </c>
       <c r="B176" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C176" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D176" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4935,13 +4944,13 @@
         <v>177</v>
       </c>
       <c r="B177" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C177" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D177" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4949,13 +4958,13 @@
         <v>178</v>
       </c>
       <c r="B178" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C178" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D178" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4963,13 +4972,13 @@
         <v>179</v>
       </c>
       <c r="B179" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C179" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D179" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4977,13 +4986,13 @@
         <v>180</v>
       </c>
       <c r="B180" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C180" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D180" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4991,13 +5000,13 @@
         <v>181</v>
       </c>
       <c r="B181" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C181" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D181" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -5005,13 +5014,13 @@
         <v>182</v>
       </c>
       <c r="B182" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C182" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D182" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5019,13 +5028,13 @@
         <v>183</v>
       </c>
       <c r="B183" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C183" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D183" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5033,13 +5042,13 @@
         <v>184</v>
       </c>
       <c r="B184" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C184" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D184" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5047,13 +5056,13 @@
         <v>185</v>
       </c>
       <c r="B185" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C185" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D185" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5061,13 +5070,13 @@
         <v>186</v>
       </c>
       <c r="B186" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C186" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D186" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5075,13 +5084,13 @@
         <v>187</v>
       </c>
       <c r="B187" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C187" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D187" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5089,13 +5098,13 @@
         <v>188</v>
       </c>
       <c r="B188" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C188" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D188" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5103,13 +5112,13 @@
         <v>189</v>
       </c>
       <c r="B189" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C189" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D189" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5117,13 +5126,13 @@
         <v>190</v>
       </c>
       <c r="B190" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C190" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D190" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5131,13 +5140,13 @@
         <v>191</v>
       </c>
       <c r="B191" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C191" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D191" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5145,13 +5154,13 @@
         <v>192</v>
       </c>
       <c r="B192" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C192" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D192" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5159,13 +5168,13 @@
         <v>193</v>
       </c>
       <c r="B193" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C193" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D193" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5173,13 +5182,13 @@
         <v>194</v>
       </c>
       <c r="B194" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C194" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D194" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5187,13 +5196,13 @@
         <v>195</v>
       </c>
       <c r="B195" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C195" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D195" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5201,13 +5210,13 @@
         <v>196</v>
       </c>
       <c r="B196" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C196" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D196" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5215,13 +5224,13 @@
         <v>197</v>
       </c>
       <c r="B197" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C197" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D197" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5229,13 +5238,13 @@
         <v>198</v>
       </c>
       <c r="B198" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C198" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D198" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5243,13 +5252,13 @@
         <v>199</v>
       </c>
       <c r="B199" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C199" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D199" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5257,13 +5266,13 @@
         <v>200</v>
       </c>
       <c r="B200" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C200" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D200" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5271,13 +5280,13 @@
         <v>201</v>
       </c>
       <c r="B201" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C201" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D201" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5285,13 +5294,13 @@
         <v>202</v>
       </c>
       <c r="B202" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C202" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D202" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5299,13 +5308,13 @@
         <v>203</v>
       </c>
       <c r="B203" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C203" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D203" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5313,13 +5322,13 @@
         <v>204</v>
       </c>
       <c r="B204" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C204" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D204" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5327,13 +5336,13 @@
         <v>205</v>
       </c>
       <c r="B205" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C205" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D205" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5341,13 +5350,13 @@
         <v>206</v>
       </c>
       <c r="B206" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C206" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D206" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5355,13 +5364,13 @@
         <v>207</v>
       </c>
       <c r="B207" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C207" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D207" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5369,13 +5378,13 @@
         <v>208</v>
       </c>
       <c r="B208" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C208" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D208" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5383,13 +5392,13 @@
         <v>209</v>
       </c>
       <c r="B209" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C209" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D209" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5397,13 +5406,13 @@
         <v>210</v>
       </c>
       <c r="B210" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C210" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D210" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5411,13 +5420,13 @@
         <v>211</v>
       </c>
       <c r="B211" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C211" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D211" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5425,13 +5434,13 @@
         <v>212</v>
       </c>
       <c r="B212" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C212" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D212" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5439,13 +5448,13 @@
         <v>213</v>
       </c>
       <c r="B213" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C213" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D213" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5453,13 +5462,13 @@
         <v>214</v>
       </c>
       <c r="B214" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C214" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D214" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5467,13 +5476,13 @@
         <v>215</v>
       </c>
       <c r="B215" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C215" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D215" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5481,13 +5490,13 @@
         <v>216</v>
       </c>
       <c r="B216" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C216" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D216" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5495,13 +5504,13 @@
         <v>217</v>
       </c>
       <c r="B217" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C217" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D217" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5509,13 +5518,13 @@
         <v>218</v>
       </c>
       <c r="B218" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C218" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D218" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5523,13 +5532,13 @@
         <v>219</v>
       </c>
       <c r="B219" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C219" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D219" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5537,13 +5546,13 @@
         <v>220</v>
       </c>
       <c r="B220" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C220" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D220" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5551,13 +5560,13 @@
         <v>221</v>
       </c>
       <c r="B221" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C221" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D221" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5565,13 +5574,13 @@
         <v>222</v>
       </c>
       <c r="B222" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C222" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D222" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5579,13 +5588,13 @@
         <v>223</v>
       </c>
       <c r="B223" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C223" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D223" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5593,13 +5602,13 @@
         <v>224</v>
       </c>
       <c r="B224" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C224" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D224" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5607,13 +5616,13 @@
         <v>225</v>
       </c>
       <c r="B225" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C225" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D225" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5621,13 +5630,13 @@
         <v>226</v>
       </c>
       <c r="B226" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C226" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D226" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5635,13 +5644,13 @@
         <v>227</v>
       </c>
       <c r="B227" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C227" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D227" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5649,13 +5658,13 @@
         <v>228</v>
       </c>
       <c r="B228" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C228" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D228" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5663,13 +5672,13 @@
         <v>229</v>
       </c>
       <c r="B229" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C229" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D229" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5677,13 +5686,13 @@
         <v>230</v>
       </c>
       <c r="B230" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C230" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D230" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5691,13 +5700,13 @@
         <v>231</v>
       </c>
       <c r="B231" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C231" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D231" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5705,13 +5714,13 @@
         <v>232</v>
       </c>
       <c r="B232" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C232" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D232" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5725,7 +5734,7 @@
         <v>233</v>
       </c>
       <c r="D233" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5739,7 +5748,7 @@
         <v>234</v>
       </c>
       <c r="D234" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5747,13 +5756,13 @@
         <v>235</v>
       </c>
       <c r="B235" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C235" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D235" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5761,13 +5770,13 @@
         <v>236</v>
       </c>
       <c r="B236" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C236" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D236" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5775,13 +5784,27 @@
         <v>237</v>
       </c>
       <c r="B237" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C237" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D237" t="s">
-        <v>705</v>
+        <v>707</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" t="s">
+        <v>238</v>
+      </c>
+      <c r="B238" t="s">
+        <v>471</v>
+      </c>
+      <c r="C238" t="s">
+        <v>471</v>
+      </c>
+      <c r="D238" t="s">
+        <v>708</v>
       </c>
     </row>
   </sheetData>

--- a/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
+++ b/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="712">
   <si>
     <t>Tên Siêu thị</t>
   </si>
@@ -733,6 +733,9 @@
     <t>KFM_BDU_DAN - R01.14 Block A2 Charm Ruby</t>
   </si>
   <si>
+    <t>KFM_HCM_Q08 - A6-7 Block A Diamond Lotus Riverside</t>
+  </si>
+  <si>
     <t>A101</t>
   </si>
   <si>
@@ -1432,6 +1435,9 @@
     <t>A262</t>
   </si>
   <si>
+    <t>A243</t>
+  </si>
+  <si>
     <t>-4970846623</t>
   </si>
   <si>
@@ -2141,6 +2147,9 @@
   </si>
   <si>
     <t>-1004438420846</t>
+  </si>
+  <si>
+    <t>-1003932619661</t>
   </si>
 </sst>
 </file>
@@ -2472,7 +2481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D238"/>
+  <dimension ref="A1:D239"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2494,13 +2503,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2508,13 +2517,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2522,13 +2531,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D4" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2536,13 +2545,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D5" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2550,13 +2559,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2564,13 +2573,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2578,13 +2587,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D8" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2592,13 +2601,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D9" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2606,13 +2615,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2620,13 +2629,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D11" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2634,13 +2643,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D12" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2648,13 +2657,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D13" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2662,13 +2671,13 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D14" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2676,13 +2685,13 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D15" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2690,13 +2699,13 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D16" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2704,13 +2713,13 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D17" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2718,13 +2727,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D18" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2732,13 +2741,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D19" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2746,13 +2755,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C20" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D20" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2760,13 +2769,13 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C21" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D21" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2774,13 +2783,13 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D22" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2788,13 +2797,13 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D23" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2802,13 +2811,13 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D24" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2816,13 +2825,13 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2830,13 +2839,13 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D26" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2844,13 +2853,13 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C27" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D27" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2858,13 +2867,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D28" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2872,13 +2881,13 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C29" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D29" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2886,13 +2895,13 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C30" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2900,13 +2909,13 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C31" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2914,13 +2923,13 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C32" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D32" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2928,13 +2937,13 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C33" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D33" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2942,13 +2951,13 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C34" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D34" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2956,13 +2965,13 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C35" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D35" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2970,13 +2979,13 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C36" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D36" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2984,13 +2993,13 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C37" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D37" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2998,13 +3007,13 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C38" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D38" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3012,13 +3021,13 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C39" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D39" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3026,13 +3035,13 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C40" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D40" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3040,13 +3049,13 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C41" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D41" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3054,13 +3063,13 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C42" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D42" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3068,13 +3077,13 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C43" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D43" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3082,13 +3091,13 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C44" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D44" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3096,13 +3105,13 @@
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C45" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D45" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3110,13 +3119,13 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C46" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D46" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3124,13 +3133,13 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C47" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D47" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3138,13 +3147,13 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C48" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D48" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3152,13 +3161,13 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C49" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D49" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3166,13 +3175,13 @@
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C50" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D50" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3180,13 +3189,13 @@
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C51" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D51" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3194,13 +3203,13 @@
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C52" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D52" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3208,13 +3217,13 @@
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C53" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D53" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3222,13 +3231,13 @@
         <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C54" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D54" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3236,13 +3245,13 @@
         <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C55" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D55" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3250,13 +3259,13 @@
         <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C56" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D56" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3264,13 +3273,13 @@
         <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C57" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D57" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3278,13 +3287,13 @@
         <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C58" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D58" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3292,13 +3301,13 @@
         <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C59" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D59" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3306,13 +3315,13 @@
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C60" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D60" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3320,13 +3329,13 @@
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C61" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D61" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3334,13 +3343,13 @@
         <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C62" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D62" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3348,13 +3357,13 @@
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C63" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D63" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3362,13 +3371,13 @@
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C64" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D64" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3376,13 +3385,13 @@
         <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C65" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D65" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3390,13 +3399,13 @@
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C66" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D66" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3404,13 +3413,13 @@
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C67" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D67" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3418,13 +3427,13 @@
         <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C68" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D68" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3432,13 +3441,13 @@
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C69" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D69" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3446,13 +3455,13 @@
         <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C70" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D70" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3460,13 +3469,13 @@
         <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C71" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D71" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3474,13 +3483,13 @@
         <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C72" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D72" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3488,13 +3497,13 @@
         <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C73" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D73" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3502,13 +3511,13 @@
         <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C74" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D74" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3516,13 +3525,13 @@
         <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C75" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D75" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3530,13 +3539,13 @@
         <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C76" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D76" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3544,13 +3553,13 @@
         <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C77" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D77" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3558,13 +3567,13 @@
         <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C78" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D78" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3572,13 +3581,13 @@
         <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C79" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D79" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3586,13 +3595,13 @@
         <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C80" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D80" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3600,13 +3609,13 @@
         <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C81" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D81" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3614,13 +3623,13 @@
         <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C82" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D82" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3628,13 +3637,13 @@
         <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C83" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D83" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3642,13 +3651,13 @@
         <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C84" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D84" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3656,13 +3665,13 @@
         <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C85" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D85" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3670,13 +3679,13 @@
         <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C86" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D86" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3684,13 +3693,13 @@
         <v>87</v>
       </c>
       <c r="B87" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C87" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D87" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3698,13 +3707,13 @@
         <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C88" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D88" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3712,13 +3721,13 @@
         <v>89</v>
       </c>
       <c r="B89" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C89" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D89" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3726,13 +3735,13 @@
         <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C90" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D90" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3740,13 +3749,13 @@
         <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C91" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D91" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3754,13 +3763,13 @@
         <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C92" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D92" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3768,13 +3777,13 @@
         <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C93" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D93" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3782,13 +3791,13 @@
         <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C94" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D94" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3796,13 +3805,13 @@
         <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C95" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D95" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3810,13 +3819,13 @@
         <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C96" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D96" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3824,13 +3833,13 @@
         <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C97" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D97" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3838,13 +3847,13 @@
         <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C98" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D98" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3852,13 +3861,13 @@
         <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C99" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D99" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3866,13 +3875,13 @@
         <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C100" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D100" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3880,13 +3889,13 @@
         <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C101" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D101" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3894,13 +3903,13 @@
         <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C102" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D102" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3908,13 +3917,13 @@
         <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C103" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D103" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3922,13 +3931,13 @@
         <v>104</v>
       </c>
       <c r="B104" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C104" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D104" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3936,13 +3945,13 @@
         <v>105</v>
       </c>
       <c r="B105" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C105" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D105" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3950,13 +3959,13 @@
         <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C106" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D106" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3964,13 +3973,13 @@
         <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C107" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D107" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3978,13 +3987,13 @@
         <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C108" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D108" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3992,13 +4001,13 @@
         <v>109</v>
       </c>
       <c r="B109" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C109" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D109" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -4006,13 +4015,13 @@
         <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C110" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D110" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4020,13 +4029,13 @@
         <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C111" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D111" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4034,13 +4043,13 @@
         <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C112" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D112" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4048,13 +4057,13 @@
         <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C113" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D113" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4062,13 +4071,13 @@
         <v>114</v>
       </c>
       <c r="B114" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C114" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D114" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4076,13 +4085,13 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C115" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D115" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4090,13 +4099,13 @@
         <v>116</v>
       </c>
       <c r="B116" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C116" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D116" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4104,13 +4113,13 @@
         <v>117</v>
       </c>
       <c r="B117" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C117" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D117" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4118,13 +4127,13 @@
         <v>118</v>
       </c>
       <c r="B118" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C118" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D118" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4132,13 +4141,13 @@
         <v>119</v>
       </c>
       <c r="B119" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C119" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D119" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4146,13 +4155,13 @@
         <v>120</v>
       </c>
       <c r="B120" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C120" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D120" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4160,13 +4169,13 @@
         <v>121</v>
       </c>
       <c r="B121" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C121" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D121" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4174,13 +4183,13 @@
         <v>122</v>
       </c>
       <c r="B122" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C122" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D122" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4188,13 +4197,13 @@
         <v>123</v>
       </c>
       <c r="B123" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C123" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D123" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4202,13 +4211,13 @@
         <v>124</v>
       </c>
       <c r="B124" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C124" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D124" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4216,13 +4225,13 @@
         <v>125</v>
       </c>
       <c r="B125" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C125" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D125" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4230,13 +4239,13 @@
         <v>126</v>
       </c>
       <c r="B126" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C126" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D126" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4244,13 +4253,13 @@
         <v>127</v>
       </c>
       <c r="B127" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C127" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D127" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4258,13 +4267,13 @@
         <v>128</v>
       </c>
       <c r="B128" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C128" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D128" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4272,13 +4281,13 @@
         <v>129</v>
       </c>
       <c r="B129" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C129" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D129" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4286,13 +4295,13 @@
         <v>130</v>
       </c>
       <c r="B130" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C130" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D130" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4300,13 +4309,13 @@
         <v>131</v>
       </c>
       <c r="B131" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C131" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D131" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4314,13 +4323,13 @@
         <v>132</v>
       </c>
       <c r="B132" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C132" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D132" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4328,13 +4337,13 @@
         <v>133</v>
       </c>
       <c r="B133" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C133" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D133" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4342,13 +4351,13 @@
         <v>134</v>
       </c>
       <c r="B134" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C134" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D134" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4356,13 +4365,13 @@
         <v>135</v>
       </c>
       <c r="B135" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C135" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D135" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4370,13 +4379,13 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C136" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D136" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4384,13 +4393,13 @@
         <v>137</v>
       </c>
       <c r="B137" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C137" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D137" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4398,13 +4407,13 @@
         <v>138</v>
       </c>
       <c r="B138" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C138" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D138" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4412,13 +4421,13 @@
         <v>139</v>
       </c>
       <c r="B139" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C139" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D139" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4426,13 +4435,13 @@
         <v>140</v>
       </c>
       <c r="B140" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C140" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D140" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4440,13 +4449,13 @@
         <v>141</v>
       </c>
       <c r="B141" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C141" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D141" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4454,13 +4463,13 @@
         <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C142" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D142" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4468,13 +4477,13 @@
         <v>143</v>
       </c>
       <c r="B143" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C143" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D143" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4482,13 +4491,13 @@
         <v>144</v>
       </c>
       <c r="B144" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C144" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D144" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4496,13 +4505,13 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C145" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D145" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4510,13 +4519,13 @@
         <v>146</v>
       </c>
       <c r="B146" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C146" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D146" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4524,13 +4533,13 @@
         <v>147</v>
       </c>
       <c r="B147" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C147" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D147" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4538,13 +4547,13 @@
         <v>148</v>
       </c>
       <c r="B148" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C148" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D148" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4552,13 +4561,13 @@
         <v>149</v>
       </c>
       <c r="B149" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C149" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D149" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4566,13 +4575,13 @@
         <v>150</v>
       </c>
       <c r="B150" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C150" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D150" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4580,13 +4589,13 @@
         <v>151</v>
       </c>
       <c r="B151" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C151" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D151" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4594,13 +4603,13 @@
         <v>152</v>
       </c>
       <c r="B152" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C152" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D152" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4608,13 +4617,13 @@
         <v>153</v>
       </c>
       <c r="B153" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C153" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D153" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4622,13 +4631,13 @@
         <v>154</v>
       </c>
       <c r="B154" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C154" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D154" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4636,13 +4645,13 @@
         <v>155</v>
       </c>
       <c r="B155" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C155" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D155" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4650,13 +4659,13 @@
         <v>156</v>
       </c>
       <c r="B156" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C156" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D156" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4664,13 +4673,13 @@
         <v>157</v>
       </c>
       <c r="B157" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C157" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D157" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4678,13 +4687,13 @@
         <v>158</v>
       </c>
       <c r="B158" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C158" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D158" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4692,13 +4701,13 @@
         <v>159</v>
       </c>
       <c r="B159" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C159" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D159" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4706,13 +4715,13 @@
         <v>160</v>
       </c>
       <c r="B160" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C160" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D160" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4720,13 +4729,13 @@
         <v>161</v>
       </c>
       <c r="B161" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C161" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D161" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4734,13 +4743,13 @@
         <v>162</v>
       </c>
       <c r="B162" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C162" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D162" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4748,13 +4757,13 @@
         <v>163</v>
       </c>
       <c r="B163" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C163" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D163" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4762,13 +4771,13 @@
         <v>164</v>
       </c>
       <c r="B164" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C164" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D164" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4776,13 +4785,13 @@
         <v>165</v>
       </c>
       <c r="B165" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C165" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D165" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4790,13 +4799,13 @@
         <v>166</v>
       </c>
       <c r="B166" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C166" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D166" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4804,13 +4813,13 @@
         <v>167</v>
       </c>
       <c r="B167" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C167" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D167" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4818,13 +4827,13 @@
         <v>168</v>
       </c>
       <c r="B168" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C168" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D168" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4832,13 +4841,13 @@
         <v>169</v>
       </c>
       <c r="B169" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C169" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D169" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4846,13 +4855,13 @@
         <v>170</v>
       </c>
       <c r="B170" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C170" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D170" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4860,13 +4869,13 @@
         <v>171</v>
       </c>
       <c r="B171" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C171" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D171" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4874,13 +4883,13 @@
         <v>172</v>
       </c>
       <c r="B172" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C172" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D172" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4888,13 +4897,13 @@
         <v>173</v>
       </c>
       <c r="B173" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C173" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D173" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4902,13 +4911,13 @@
         <v>174</v>
       </c>
       <c r="B174" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C174" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D174" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4916,13 +4925,13 @@
         <v>175</v>
       </c>
       <c r="B175" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C175" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D175" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4930,13 +4939,13 @@
         <v>176</v>
       </c>
       <c r="B176" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C176" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D176" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4944,13 +4953,13 @@
         <v>177</v>
       </c>
       <c r="B177" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C177" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D177" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4958,13 +4967,13 @@
         <v>178</v>
       </c>
       <c r="B178" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C178" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D178" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4972,13 +4981,13 @@
         <v>179</v>
       </c>
       <c r="B179" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C179" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D179" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4986,13 +4995,13 @@
         <v>180</v>
       </c>
       <c r="B180" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C180" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D180" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -5000,13 +5009,13 @@
         <v>181</v>
       </c>
       <c r="B181" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C181" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D181" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -5014,13 +5023,13 @@
         <v>182</v>
       </c>
       <c r="B182" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C182" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D182" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5028,13 +5037,13 @@
         <v>183</v>
       </c>
       <c r="B183" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C183" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D183" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5042,13 +5051,13 @@
         <v>184</v>
       </c>
       <c r="B184" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C184" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D184" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5056,13 +5065,13 @@
         <v>185</v>
       </c>
       <c r="B185" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C185" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D185" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5070,13 +5079,13 @@
         <v>186</v>
       </c>
       <c r="B186" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C186" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D186" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5084,13 +5093,13 @@
         <v>187</v>
       </c>
       <c r="B187" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C187" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D187" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5098,13 +5107,13 @@
         <v>188</v>
       </c>
       <c r="B188" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C188" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D188" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5112,13 +5121,13 @@
         <v>189</v>
       </c>
       <c r="B189" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C189" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D189" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5126,13 +5135,13 @@
         <v>190</v>
       </c>
       <c r="B190" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C190" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D190" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5140,13 +5149,13 @@
         <v>191</v>
       </c>
       <c r="B191" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C191" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D191" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5154,13 +5163,13 @@
         <v>192</v>
       </c>
       <c r="B192" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C192" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D192" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5168,13 +5177,13 @@
         <v>193</v>
       </c>
       <c r="B193" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C193" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D193" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5182,13 +5191,13 @@
         <v>194</v>
       </c>
       <c r="B194" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C194" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D194" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5196,13 +5205,13 @@
         <v>195</v>
       </c>
       <c r="B195" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C195" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D195" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5210,13 +5219,13 @@
         <v>196</v>
       </c>
       <c r="B196" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C196" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D196" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5224,13 +5233,13 @@
         <v>197</v>
       </c>
       <c r="B197" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C197" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D197" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5238,13 +5247,13 @@
         <v>198</v>
       </c>
       <c r="B198" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C198" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D198" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5252,13 +5261,13 @@
         <v>199</v>
       </c>
       <c r="B199" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C199" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D199" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5266,13 +5275,13 @@
         <v>200</v>
       </c>
       <c r="B200" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C200" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D200" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5280,13 +5289,13 @@
         <v>201</v>
       </c>
       <c r="B201" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C201" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D201" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5294,13 +5303,13 @@
         <v>202</v>
       </c>
       <c r="B202" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C202" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D202" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5308,13 +5317,13 @@
         <v>203</v>
       </c>
       <c r="B203" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C203" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D203" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5322,13 +5331,13 @@
         <v>204</v>
       </c>
       <c r="B204" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C204" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D204" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5336,13 +5345,13 @@
         <v>205</v>
       </c>
       <c r="B205" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C205" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D205" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5350,13 +5359,13 @@
         <v>206</v>
       </c>
       <c r="B206" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C206" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D206" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5364,13 +5373,13 @@
         <v>207</v>
       </c>
       <c r="B207" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C207" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D207" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5378,13 +5387,13 @@
         <v>208</v>
       </c>
       <c r="B208" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C208" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D208" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5392,13 +5401,13 @@
         <v>209</v>
       </c>
       <c r="B209" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C209" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D209" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5406,13 +5415,13 @@
         <v>210</v>
       </c>
       <c r="B210" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C210" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D210" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5420,13 +5429,13 @@
         <v>211</v>
       </c>
       <c r="B211" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C211" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D211" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5434,13 +5443,13 @@
         <v>212</v>
       </c>
       <c r="B212" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C212" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D212" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5448,13 +5457,13 @@
         <v>213</v>
       </c>
       <c r="B213" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C213" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D213" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5462,13 +5471,13 @@
         <v>214</v>
       </c>
       <c r="B214" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C214" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D214" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5476,13 +5485,13 @@
         <v>215</v>
       </c>
       <c r="B215" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C215" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D215" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5490,13 +5499,13 @@
         <v>216</v>
       </c>
       <c r="B216" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C216" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D216" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5504,13 +5513,13 @@
         <v>217</v>
       </c>
       <c r="B217" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C217" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D217" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5518,13 +5527,13 @@
         <v>218</v>
       </c>
       <c r="B218" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C218" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D218" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5532,13 +5541,13 @@
         <v>219</v>
       </c>
       <c r="B219" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C219" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D219" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5546,13 +5555,13 @@
         <v>220</v>
       </c>
       <c r="B220" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C220" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D220" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5560,13 +5569,13 @@
         <v>221</v>
       </c>
       <c r="B221" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C221" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D221" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5574,13 +5583,13 @@
         <v>222</v>
       </c>
       <c r="B222" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C222" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D222" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5588,13 +5597,13 @@
         <v>223</v>
       </c>
       <c r="B223" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C223" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D223" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5602,13 +5611,13 @@
         <v>224</v>
       </c>
       <c r="B224" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C224" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D224" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5616,13 +5625,13 @@
         <v>225</v>
       </c>
       <c r="B225" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C225" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D225" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5630,13 +5639,13 @@
         <v>226</v>
       </c>
       <c r="B226" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C226" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D226" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5644,13 +5653,13 @@
         <v>227</v>
       </c>
       <c r="B227" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C227" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D227" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5658,13 +5667,13 @@
         <v>228</v>
       </c>
       <c r="B228" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C228" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D228" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5672,13 +5681,13 @@
         <v>229</v>
       </c>
       <c r="B229" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C229" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D229" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5686,13 +5695,13 @@
         <v>230</v>
       </c>
       <c r="B230" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C230" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D230" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5700,13 +5709,13 @@
         <v>231</v>
       </c>
       <c r="B231" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C231" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D231" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5714,13 +5723,13 @@
         <v>232</v>
       </c>
       <c r="B232" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C232" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D232" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5734,7 +5743,7 @@
         <v>233</v>
       </c>
       <c r="D233" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5748,7 +5757,7 @@
         <v>234</v>
       </c>
       <c r="D234" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5756,13 +5765,13 @@
         <v>235</v>
       </c>
       <c r="B235" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C235" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D235" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5770,13 +5779,13 @@
         <v>236</v>
       </c>
       <c r="B236" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C236" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D236" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5784,13 +5793,13 @@
         <v>237</v>
       </c>
       <c r="B237" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C237" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D237" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5798,13 +5807,27 @@
         <v>238</v>
       </c>
       <c r="B238" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C238" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D238" t="s">
-        <v>708</v>
+        <v>710</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" t="s">
+        <v>239</v>
+      </c>
+      <c r="B239" t="s">
+        <v>473</v>
+      </c>
+      <c r="C239" t="s">
+        <v>473</v>
+      </c>
+      <c r="D239" t="s">
+        <v>711</v>
       </c>
     </row>
   </sheetData>

--- a/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
+++ b/SPAM_PHIEU_CHUYEN/CONFIG_DATA/Danh_Sach_Sieu_Thi_Dong_Mat.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="715">
   <si>
     <t>Tên Siêu thị</t>
   </si>
@@ -736,6 +736,9 @@
     <t>KFM_HCM_Q08 - A6-7 Block A Diamond Lotus Riverside</t>
   </si>
   <si>
+    <t>KFM_HCM_BCH - CA.01 Đường 19 KDC Phong Phú 4</t>
+  </si>
+  <si>
     <t>A101</t>
   </si>
   <si>
@@ -1438,6 +1441,9 @@
     <t>A243</t>
   </si>
   <si>
+    <t>A216</t>
+  </si>
+  <si>
     <t>-4970846623</t>
   </si>
   <si>
@@ -2150,6 +2156,9 @@
   </si>
   <si>
     <t>-1003932619661</t>
+  </si>
+  <si>
+    <t>-1004361944433</t>
   </si>
 </sst>
 </file>
@@ -2481,7 +2490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D239"/>
+  <dimension ref="A1:D240"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2503,13 +2512,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2517,13 +2526,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2531,13 +2540,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D4" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2545,13 +2554,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D5" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2559,13 +2568,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2573,13 +2582,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D7" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2587,13 +2596,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D8" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2601,13 +2610,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D9" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2615,13 +2624,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D10" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2629,13 +2638,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D11" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2643,13 +2652,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D12" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2657,13 +2666,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D13" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2671,13 +2680,13 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D14" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2685,13 +2694,13 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D15" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2699,13 +2708,13 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D16" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2713,13 +2722,13 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D17" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2727,13 +2736,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D18" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2741,13 +2750,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D19" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2755,13 +2764,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D20" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2769,13 +2778,13 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D21" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2783,13 +2792,13 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D22" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2797,13 +2806,13 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D23" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2811,13 +2820,13 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2825,13 +2834,13 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D25" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2839,13 +2848,13 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C26" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D26" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2853,13 +2862,13 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C27" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D27" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2867,13 +2876,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C28" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D28" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2881,13 +2890,13 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C29" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2895,13 +2904,13 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D30" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2909,13 +2918,13 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D31" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2923,13 +2932,13 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C32" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D32" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2937,13 +2946,13 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C33" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D33" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2951,13 +2960,13 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C34" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D34" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2965,13 +2974,13 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C35" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D35" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2979,13 +2988,13 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C36" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D36" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2993,13 +3002,13 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C37" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D37" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3007,13 +3016,13 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C38" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D38" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3021,13 +3030,13 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C39" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D39" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3035,13 +3044,13 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C40" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D40" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3049,13 +3058,13 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C41" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D41" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3063,13 +3072,13 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C42" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D42" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3077,13 +3086,13 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D43" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3091,13 +3100,13 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C44" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D44" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3105,13 +3114,13 @@
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D45" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3119,13 +3128,13 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C46" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D46" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3133,13 +3142,13 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C47" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D47" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3147,13 +3156,13 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C48" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D48" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3161,13 +3170,13 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C49" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D49" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3175,13 +3184,13 @@
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C50" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D50" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3189,13 +3198,13 @@
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C51" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D51" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3203,13 +3212,13 @@
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C52" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D52" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3217,13 +3226,13 @@
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C53" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D53" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3231,13 +3240,13 @@
         <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C54" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D54" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3245,13 +3254,13 @@
         <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C55" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D55" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3259,13 +3268,13 @@
         <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C56" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D56" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3273,13 +3282,13 @@
         <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C57" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D57" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3287,13 +3296,13 @@
         <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C58" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D58" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3301,13 +3310,13 @@
         <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C59" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D59" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3315,13 +3324,13 @@
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C60" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D60" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3329,13 +3338,13 @@
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C61" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D61" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3343,13 +3352,13 @@
         <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C62" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D62" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3357,13 +3366,13 @@
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C63" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D63" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3371,13 +3380,13 @@
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C64" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D64" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3385,13 +3394,13 @@
         <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C65" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D65" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3399,13 +3408,13 @@
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C66" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D66" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3413,13 +3422,13 @@
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C67" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D67" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3427,13 +3436,13 @@
         <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C68" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D68" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3441,13 +3450,13 @@
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C69" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D69" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3455,13 +3464,13 @@
         <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C70" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D70" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3469,13 +3478,13 @@
         <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C71" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D71" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3483,13 +3492,13 @@
         <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C72" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D72" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3497,13 +3506,13 @@
         <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C73" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D73" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3511,13 +3520,13 @@
         <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C74" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D74" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3525,13 +3534,13 @@
         <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C75" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D75" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3539,13 +3548,13 @@
         <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C76" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D76" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3553,13 +3562,13 @@
         <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C77" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D77" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3567,13 +3576,13 @@
         <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C78" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D78" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3581,13 +3590,13 @@
         <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C79" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D79" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3595,13 +3604,13 @@
         <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C80" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D80" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3609,13 +3618,13 @@
         <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C81" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D81" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3623,13 +3632,13 @@
         <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C82" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D82" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3637,13 +3646,13 @@
         <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C83" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D83" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3651,13 +3660,13 @@
         <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C84" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D84" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3665,13 +3674,13 @@
         <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C85" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D85" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3679,13 +3688,13 @@
         <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C86" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D86" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3693,13 +3702,13 @@
         <v>87</v>
       </c>
       <c r="B87" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C87" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D87" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3707,13 +3716,13 @@
         <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C88" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D88" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3721,13 +3730,13 @@
         <v>89</v>
       </c>
       <c r="B89" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C89" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D89" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3735,13 +3744,13 @@
         <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C90" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D90" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3749,13 +3758,13 @@
         <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C91" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D91" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3763,13 +3772,13 @@
         <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C92" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D92" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3777,13 +3786,13 @@
         <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C93" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D93" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3791,13 +3800,13 @@
         <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C94" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D94" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3805,13 +3814,13 @@
         <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C95" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D95" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3819,13 +3828,13 @@
         <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C96" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D96" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3833,13 +3842,13 @@
         <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C97" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D97" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3847,13 +3856,13 @@
         <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C98" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D98" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3861,13 +3870,13 @@
         <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C99" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D99" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3875,13 +3884,13 @@
         <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C100" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D100" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3889,13 +3898,13 @@
         <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C101" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D101" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3903,13 +3912,13 @@
         <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C102" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D102" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3917,13 +3926,13 @@
         <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C103" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D103" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3931,13 +3940,13 @@
         <v>104</v>
       </c>
       <c r="B104" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C104" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D104" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3945,13 +3954,13 @@
         <v>105</v>
       </c>
       <c r="B105" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C105" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D105" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3959,13 +3968,13 @@
         <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C106" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D106" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3973,13 +3982,13 @@
         <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C107" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D107" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3987,13 +3996,13 @@
         <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C108" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D108" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -4001,13 +4010,13 @@
         <v>109</v>
       </c>
       <c r="B109" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C109" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D109" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -4015,13 +4024,13 @@
         <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C110" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D110" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4029,13 +4038,13 @@
         <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C111" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D111" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4043,13 +4052,13 @@
         <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C112" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D112" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4057,13 +4066,13 @@
         <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C113" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D113" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4071,13 +4080,13 @@
         <v>114</v>
       </c>
       <c r="B114" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C114" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D114" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4085,13 +4094,13 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C115" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D115" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4099,13 +4108,13 @@
         <v>116</v>
       </c>
       <c r="B116" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C116" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D116" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4113,13 +4122,13 @@
         <v>117</v>
       </c>
       <c r="B117" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C117" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D117" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4127,13 +4136,13 @@
         <v>118</v>
       </c>
       <c r="B118" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C118" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D118" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4141,13 +4150,13 @@
         <v>119</v>
       </c>
       <c r="B119" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C119" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D119" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4155,13 +4164,13 @@
         <v>120</v>
       </c>
       <c r="B120" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C120" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D120" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4169,13 +4178,13 @@
         <v>121</v>
       </c>
       <c r="B121" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C121" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D121" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4183,13 +4192,13 @@
         <v>122</v>
       </c>
       <c r="B122" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C122" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D122" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4197,13 +4206,13 @@
         <v>123</v>
       </c>
       <c r="B123" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C123" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D123" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4211,13 +4220,13 @@
         <v>124</v>
       </c>
       <c r="B124" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C124" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D124" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4225,13 +4234,13 @@
         <v>125</v>
       </c>
       <c r="B125" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C125" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D125" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4239,13 +4248,13 @@
         <v>126</v>
       </c>
       <c r="B126" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C126" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D126" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4253,13 +4262,13 @@
         <v>127</v>
       </c>
       <c r="B127" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C127" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D127" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4267,13 +4276,13 @@
         <v>128</v>
       </c>
       <c r="B128" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C128" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D128" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4281,13 +4290,13 @@
         <v>129</v>
       </c>
       <c r="B129" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C129" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D129" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4295,13 +4304,13 @@
         <v>130</v>
       </c>
       <c r="B130" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C130" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D130" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4309,13 +4318,13 @@
         <v>131</v>
       </c>
       <c r="B131" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C131" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D131" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4323,13 +4332,13 @@
         <v>132</v>
       </c>
       <c r="B132" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C132" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D132" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4337,13 +4346,13 @@
         <v>133</v>
       </c>
       <c r="B133" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C133" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D133" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4351,13 +4360,13 @@
         <v>134</v>
       </c>
       <c r="B134" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C134" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D134" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4365,13 +4374,13 @@
         <v>135</v>
       </c>
       <c r="B135" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C135" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D135" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4379,13 +4388,13 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C136" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D136" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4393,13 +4402,13 @@
         <v>137</v>
       </c>
       <c r="B137" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C137" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D137" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4407,13 +4416,13 @@
         <v>138</v>
       </c>
       <c r="B138" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C138" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D138" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4421,13 +4430,13 @@
         <v>139</v>
       </c>
       <c r="B139" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C139" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D139" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4435,13 +4444,13 @@
         <v>140</v>
       </c>
       <c r="B140" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C140" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D140" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4449,13 +4458,13 @@
         <v>141</v>
       </c>
       <c r="B141" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C141" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D141" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4463,13 +4472,13 @@
         <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C142" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D142" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4477,13 +4486,13 @@
         <v>143</v>
       </c>
       <c r="B143" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C143" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D143" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4491,13 +4500,13 @@
         <v>144</v>
       </c>
       <c r="B144" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C144" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D144" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4505,13 +4514,13 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C145" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D145" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4519,13 +4528,13 @@
         <v>146</v>
       </c>
       <c r="B146" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C146" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D146" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4533,13 +4542,13 @@
         <v>147</v>
       </c>
       <c r="B147" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C147" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D147" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4547,13 +4556,13 @@
         <v>148</v>
       </c>
       <c r="B148" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C148" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D148" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4561,13 +4570,13 @@
         <v>149</v>
       </c>
       <c r="B149" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C149" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D149" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4575,13 +4584,13 @@
         <v>150</v>
       </c>
       <c r="B150" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C150" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D150" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4589,13 +4598,13 @@
         <v>151</v>
       </c>
       <c r="B151" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C151" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D151" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4603,13 +4612,13 @@
         <v>152</v>
       </c>
       <c r="B152" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C152" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D152" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4617,13 +4626,13 @@
         <v>153</v>
       </c>
       <c r="B153" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C153" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D153" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4631,13 +4640,13 @@
         <v>154</v>
       </c>
       <c r="B154" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C154" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D154" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4645,13 +4654,13 @@
         <v>155</v>
       </c>
       <c r="B155" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C155" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D155" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4659,13 +4668,13 @@
         <v>156</v>
       </c>
       <c r="B156" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C156" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D156" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4673,13 +4682,13 @@
         <v>157</v>
       </c>
       <c r="B157" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C157" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D157" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4687,13 +4696,13 @@
         <v>158</v>
       </c>
       <c r="B158" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C158" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D158" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4701,13 +4710,13 @@
         <v>159</v>
       </c>
       <c r="B159" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C159" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D159" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4715,13 +4724,13 @@
         <v>160</v>
       </c>
       <c r="B160" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C160" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D160" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4729,13 +4738,13 @@
         <v>161</v>
       </c>
       <c r="B161" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C161" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D161" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4743,13 +4752,13 @@
         <v>162</v>
       </c>
       <c r="B162" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C162" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D162" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4757,13 +4766,13 @@
         <v>163</v>
       </c>
       <c r="B163" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C163" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D163" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4771,13 +4780,13 @@
         <v>164</v>
       </c>
       <c r="B164" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C164" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D164" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4785,13 +4794,13 @@
         <v>165</v>
       </c>
       <c r="B165" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C165" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D165" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4799,13 +4808,13 @@
         <v>166</v>
       </c>
       <c r="B166" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C166" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D166" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4813,13 +4822,13 @@
         <v>167</v>
       </c>
       <c r="B167" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C167" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D167" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4827,13 +4836,13 @@
         <v>168</v>
       </c>
       <c r="B168" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C168" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D168" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4841,13 +4850,13 @@
         <v>169</v>
       </c>
       <c r="B169" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C169" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D169" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4855,13 +4864,13 @@
         <v>170</v>
       </c>
       <c r="B170" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C170" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D170" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4869,13 +4878,13 @@
         <v>171</v>
       </c>
       <c r="B171" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C171" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D171" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4883,13 +4892,13 @@
         <v>172</v>
       </c>
       <c r="B172" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C172" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D172" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4897,13 +4906,13 @@
         <v>173</v>
       </c>
       <c r="B173" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C173" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D173" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4911,13 +4920,13 @@
         <v>174</v>
       </c>
       <c r="B174" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C174" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D174" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4925,13 +4934,13 @@
         <v>175</v>
       </c>
       <c r="B175" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C175" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D175" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4939,13 +4948,13 @@
         <v>176</v>
       </c>
       <c r="B176" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C176" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D176" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4953,13 +4962,13 @@
         <v>177</v>
       </c>
       <c r="B177" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C177" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D177" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4967,13 +4976,13 @@
         <v>178</v>
       </c>
       <c r="B178" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C178" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D178" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4981,13 +4990,13 @@
         <v>179</v>
       </c>
       <c r="B179" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C179" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D179" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4995,13 +5004,13 @@
         <v>180</v>
       </c>
       <c r="B180" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C180" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D180" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -5009,13 +5018,13 @@
         <v>181</v>
       </c>
       <c r="B181" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C181" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D181" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -5023,13 +5032,13 @@
         <v>182</v>
       </c>
       <c r="B182" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C182" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D182" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5037,13 +5046,13 @@
         <v>183</v>
       </c>
       <c r="B183" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C183" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D183" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5051,13 +5060,13 @@
         <v>184</v>
       </c>
       <c r="B184" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C184" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D184" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5065,13 +5074,13 @@
         <v>185</v>
       </c>
       <c r="B185" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C185" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D185" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5079,13 +5088,13 @@
         <v>186</v>
       </c>
       <c r="B186" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C186" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D186" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5093,13 +5102,13 @@
         <v>187</v>
       </c>
       <c r="B187" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C187" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D187" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5107,13 +5116,13 @@
         <v>188</v>
       </c>
       <c r="B188" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C188" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D188" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5121,13 +5130,13 @@
         <v>189</v>
       </c>
       <c r="B189" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C189" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D189" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5135,13 +5144,13 @@
         <v>190</v>
       </c>
       <c r="B190" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C190" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D190" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5149,13 +5158,13 @@
         <v>191</v>
       </c>
       <c r="B191" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C191" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D191" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5163,13 +5172,13 @@
         <v>192</v>
       </c>
       <c r="B192" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C192" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D192" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5177,13 +5186,13 @@
         <v>193</v>
       </c>
       <c r="B193" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C193" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D193" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5191,13 +5200,13 @@
         <v>194</v>
       </c>
       <c r="B194" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C194" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D194" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5205,13 +5214,13 @@
         <v>195</v>
       </c>
       <c r="B195" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C195" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D195" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5219,13 +5228,13 @@
         <v>196</v>
       </c>
       <c r="B196" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C196" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D196" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5233,13 +5242,13 @@
         <v>197</v>
       </c>
       <c r="B197" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C197" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D197" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5247,13 +5256,13 @@
         <v>198</v>
       </c>
       <c r="B198" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C198" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D198" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5261,13 +5270,13 @@
         <v>199</v>
       </c>
       <c r="B199" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C199" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D199" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5275,13 +5284,13 @@
         <v>200</v>
       </c>
       <c r="B200" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C200" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D200" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5289,13 +5298,13 @@
         <v>201</v>
       </c>
       <c r="B201" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C201" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D201" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5303,13 +5312,13 @@
         <v>202</v>
       </c>
       <c r="B202" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C202" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D202" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5317,13 +5326,13 @@
         <v>203</v>
       </c>
       <c r="B203" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C203" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D203" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5331,13 +5340,13 @@
         <v>204</v>
       </c>
       <c r="B204" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C204" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D204" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5345,13 +5354,13 @@
         <v>205</v>
       </c>
       <c r="B205" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C205" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D205" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5359,13 +5368,13 @@
         <v>206</v>
       </c>
       <c r="B206" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C206" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D206" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5373,13 +5382,13 @@
         <v>207</v>
       </c>
       <c r="B207" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C207" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D207" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5387,13 +5396,13 @@
         <v>208</v>
       </c>
       <c r="B208" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C208" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D208" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5401,13 +5410,13 @@
         <v>209</v>
       </c>
       <c r="B209" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C209" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D209" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5415,13 +5424,13 @@
         <v>210</v>
       </c>
       <c r="B210" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C210" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D210" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5429,13 +5438,13 @@
         <v>211</v>
       </c>
       <c r="B211" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C211" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D211" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5443,13 +5452,13 @@
         <v>212</v>
       </c>
       <c r="B212" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C212" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D212" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5457,13 +5466,13 @@
         <v>213</v>
       </c>
       <c r="B213" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C213" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D213" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5471,13 +5480,13 @@
         <v>214</v>
       </c>
       <c r="B214" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C214" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D214" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5485,13 +5494,13 @@
         <v>215</v>
       </c>
       <c r="B215" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C215" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D215" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5499,13 +5508,13 @@
         <v>216</v>
       </c>
       <c r="B216" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C216" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D216" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5513,13 +5522,13 @@
         <v>217</v>
       </c>
       <c r="B217" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C217" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D217" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5527,13 +5536,13 @@
         <v>218</v>
       </c>
       <c r="B218" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C218" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D218" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5541,13 +5550,13 @@
         <v>219</v>
       </c>
       <c r="B219" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C219" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D219" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5555,13 +5564,13 @@
         <v>220</v>
       </c>
       <c r="B220" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C220" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D220" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5569,13 +5578,13 @@
         <v>221</v>
       </c>
       <c r="B221" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C221" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D221" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5583,13 +5592,13 @@
         <v>222</v>
       </c>
       <c r="B222" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C222" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D222" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5597,13 +5606,13 @@
         <v>223</v>
       </c>
       <c r="B223" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C223" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D223" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5611,13 +5620,13 @@
         <v>224</v>
       </c>
       <c r="B224" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C224" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D224" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5625,13 +5634,13 @@
         <v>225</v>
       </c>
       <c r="B225" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C225" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D225" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5639,13 +5648,13 @@
         <v>226</v>
       </c>
       <c r="B226" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C226" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D226" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5653,13 +5662,13 @@
         <v>227</v>
       </c>
       <c r="B227" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C227" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D227" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5667,13 +5676,13 @@
         <v>228</v>
       </c>
       <c r="B228" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C228" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D228" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5681,13 +5690,13 @@
         <v>229</v>
       </c>
       <c r="B229" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C229" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D229" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5695,13 +5704,13 @@
         <v>230</v>
       </c>
       <c r="B230" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C230" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D230" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5709,13 +5718,13 @@
         <v>231</v>
       </c>
       <c r="B231" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C231" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D231" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5723,13 +5732,13 @@
         <v>232</v>
       </c>
       <c r="B232" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C232" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D232" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5743,7 +5752,7 @@
         <v>233</v>
       </c>
       <c r="D233" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5757,7 +5766,7 @@
         <v>234</v>
       </c>
       <c r="D234" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5765,13 +5774,13 @@
         <v>235</v>
       </c>
       <c r="B235" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C235" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D235" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5779,13 +5788,13 @@
         <v>236</v>
       </c>
       <c r="B236" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C236" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D236" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5793,13 +5802,13 @@
         <v>237</v>
       </c>
       <c r="B237" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C237" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D237" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5807,13 +5816,13 @@
         <v>238</v>
       </c>
       <c r="B238" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C238" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D238" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5821,13 +5830,27 @@
         <v>239</v>
       </c>
       <c r="B239" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C239" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D239" t="s">
-        <v>711</v>
+        <v>713</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" t="s">
+        <v>240</v>
+      </c>
+      <c r="B240" t="s">
+        <v>475</v>
+      </c>
+      <c r="C240" t="s">
+        <v>475</v>
+      </c>
+      <c r="D240" t="s">
+        <v>714</v>
       </c>
     </row>
   </sheetData>
